--- a/data/base_appels_clean.xlsx
+++ b/data/base_appels_clean.xlsx
@@ -3124,3073 +3124,3073 @@
     <t>Femme</t>
   </si>
   <si>
-    <t>0747501292</t>
-  </si>
-  <si>
-    <t>0171623293</t>
-  </si>
-  <si>
-    <t>0574257526</t>
-  </si>
-  <si>
-    <t>0748053488</t>
-  </si>
-  <si>
-    <t>0749650291</t>
-  </si>
-  <si>
-    <t>0757736220</t>
-  </si>
-  <si>
-    <t>0505528100</t>
-  </si>
-  <si>
-    <t>0594312080</t>
-  </si>
-  <si>
-    <t>0768831251</t>
-  </si>
-  <si>
-    <t>0789065217</t>
-  </si>
-  <si>
-    <t>0173795629</t>
-  </si>
-  <si>
-    <t>0749898829</t>
-  </si>
-  <si>
-    <t>0564470561</t>
-  </si>
-  <si>
-    <t>0768648490</t>
-  </si>
-  <si>
-    <t>0707147940</t>
-  </si>
-  <si>
-    <t>0101575945</t>
-  </si>
-  <si>
-    <t>0708376302</t>
-  </si>
-  <si>
-    <t>0749865878</t>
-  </si>
-  <si>
-    <t>0778121588</t>
-  </si>
-  <si>
-    <t>0707944855</t>
-  </si>
-  <si>
-    <t>0709684114</t>
-  </si>
-  <si>
-    <t>0564096117</t>
-  </si>
-  <si>
-    <t>0758452997</t>
-  </si>
-  <si>
-    <t>0586509726</t>
-  </si>
-  <si>
-    <t>0769953840</t>
-  </si>
-  <si>
-    <t>0500414954</t>
-  </si>
-  <si>
-    <t>0707983480</t>
-  </si>
-  <si>
-    <t>0574482448</t>
-  </si>
-  <si>
-    <t>0584414022</t>
-  </si>
-  <si>
-    <t>0777439564</t>
-  </si>
-  <si>
-    <t>0707378488</t>
-  </si>
-  <si>
-    <t>0141848565</t>
-  </si>
-  <si>
-    <t>0151268895</t>
-  </si>
-  <si>
-    <t>0566457094</t>
-  </si>
-  <si>
-    <t>0140033847</t>
-  </si>
-  <si>
-    <t>0778210170</t>
-  </si>
-  <si>
-    <t>0142646573</t>
-  </si>
-  <si>
-    <t>0767536232</t>
-  </si>
-  <si>
-    <t>0508094980</t>
-  </si>
-  <si>
-    <t>0574871112</t>
-  </si>
-  <si>
-    <t>0565666283</t>
-  </si>
-  <si>
-    <t>0502413232</t>
-  </si>
-  <si>
-    <t>0172469131</t>
-  </si>
-  <si>
-    <t>0749000710</t>
-  </si>
-  <si>
-    <t>0505758786</t>
-  </si>
-  <si>
-    <t>0779670355</t>
-  </si>
-  <si>
-    <t>0747224512</t>
-  </si>
-  <si>
-    <t>0707586063</t>
-  </si>
-  <si>
-    <t>0545544134</t>
-  </si>
-  <si>
-    <t>0172713139</t>
-  </si>
-  <si>
-    <t>0143398350</t>
-  </si>
-  <si>
-    <t>0748445483</t>
-  </si>
-  <si>
-    <t>0779977958</t>
-  </si>
-  <si>
-    <t>0778929075</t>
-  </si>
-  <si>
-    <t>0711332409</t>
-  </si>
-  <si>
-    <t>0103259819</t>
-  </si>
-  <si>
-    <t>0101102470</t>
-  </si>
-  <si>
-    <t>0566841064</t>
-  </si>
-  <si>
-    <t>0749977282</t>
-  </si>
-  <si>
-    <t>0555581075</t>
-  </si>
-  <si>
-    <t>0152511343</t>
-  </si>
-  <si>
-    <t>0545634573</t>
-  </si>
-  <si>
-    <t>0789189652</t>
-  </si>
-  <si>
-    <t>0500907034</t>
-  </si>
-  <si>
-    <t>0153987643</t>
-  </si>
-  <si>
-    <t>0701424647</t>
-  </si>
-  <si>
-    <t>0150114233</t>
-  </si>
-  <si>
-    <t>0709924799</t>
-  </si>
-  <si>
-    <t>0700745166</t>
-  </si>
-  <si>
-    <t>0707128162</t>
-  </si>
-  <si>
-    <t>0584498648</t>
-  </si>
-  <si>
-    <t>0101507730</t>
-  </si>
-  <si>
-    <t>0701067410</t>
-  </si>
-  <si>
-    <t>0586323416</t>
-  </si>
-  <si>
-    <t>0141143692</t>
-  </si>
-  <si>
-    <t>0747021382</t>
-  </si>
-  <si>
-    <t>0787259766</t>
-  </si>
-  <si>
-    <t>0707639734</t>
-  </si>
-  <si>
-    <t>0142636781</t>
-  </si>
-  <si>
-    <t>0500218552</t>
-  </si>
-  <si>
-    <t>0748594228</t>
-  </si>
-  <si>
-    <t>0564338638</t>
-  </si>
-  <si>
-    <t>0566409361</t>
-  </si>
-  <si>
-    <t>0103292948</t>
-  </si>
-  <si>
-    <t>0505415505</t>
-  </si>
-  <si>
-    <t>0153646408</t>
-  </si>
-  <si>
-    <t>0707681513</t>
-  </si>
-  <si>
-    <t>9748646186</t>
-  </si>
-  <si>
-    <t>0777921724</t>
-  </si>
-  <si>
-    <t>0545488613</t>
-  </si>
-  <si>
-    <t>0152698760</t>
-  </si>
-  <si>
-    <t>0779645888</t>
-  </si>
-  <si>
-    <t>0708166834</t>
-  </si>
-  <si>
-    <t>0505979178</t>
-  </si>
-  <si>
-    <t>0707594181</t>
-  </si>
-  <si>
-    <t>0706143270</t>
-  </si>
-  <si>
-    <t>0544144174</t>
-  </si>
-  <si>
-    <t>0141035390</t>
-  </si>
-  <si>
-    <t>0748636067</t>
-  </si>
-  <si>
-    <t>0769364117</t>
-  </si>
-  <si>
-    <t>0711679753</t>
-  </si>
-  <si>
-    <t>0707686641</t>
-  </si>
-  <si>
-    <t>0140642969</t>
-  </si>
-  <si>
-    <t>0596933916</t>
-  </si>
-  <si>
-    <t>0152174685</t>
-  </si>
-  <si>
-    <t>0708927249</t>
-  </si>
-  <si>
-    <t>0101209890</t>
-  </si>
-  <si>
-    <t>0501646376</t>
-  </si>
-  <si>
-    <t>0502292075</t>
-  </si>
-  <si>
-    <t>0101664781</t>
-  </si>
-  <si>
-    <t>0594443529</t>
-  </si>
-  <si>
-    <t>0777790519</t>
-  </si>
-  <si>
-    <t>0506042025</t>
-  </si>
-  <si>
-    <t>0703615622</t>
-  </si>
-  <si>
-    <t>0152850005</t>
-  </si>
-  <si>
-    <t>0152822005</t>
-  </si>
-  <si>
-    <t>0706745019</t>
-  </si>
-  <si>
-    <t>0505554400</t>
-  </si>
-  <si>
-    <t>0709422480</t>
-  </si>
-  <si>
-    <t>0152025588</t>
-  </si>
-  <si>
-    <t>0742825063</t>
-  </si>
-  <si>
-    <t>0555400003</t>
-  </si>
-  <si>
-    <t>0758668459</t>
-  </si>
-  <si>
-    <t>0150477395</t>
-  </si>
-  <si>
-    <t>0555427751</t>
-  </si>
-  <si>
-    <t>0170582235</t>
-  </si>
-  <si>
-    <t>0779518545</t>
-  </si>
-  <si>
-    <t>0103222651</t>
-  </si>
-  <si>
-    <t>0171617026</t>
-  </si>
-  <si>
-    <t>0707843211</t>
-  </si>
-  <si>
-    <t>0505164901</t>
-  </si>
-  <si>
-    <t>0709892302</t>
-  </si>
-  <si>
-    <t>0505460863</t>
-  </si>
-  <si>
-    <t>0171643022</t>
-  </si>
-  <si>
-    <t>0707271248</t>
-  </si>
-  <si>
-    <t>0594880003</t>
-  </si>
-  <si>
-    <t>0565570588</t>
-  </si>
-  <si>
-    <t>0585772294</t>
-  </si>
-  <si>
-    <t>0788260914</t>
-  </si>
-  <si>
-    <t>0707282600</t>
-  </si>
-  <si>
-    <t>0101005588</t>
-  </si>
-  <si>
-    <t>0505224885</t>
-  </si>
-  <si>
-    <t>0150183926</t>
-  </si>
-  <si>
-    <t>0708344033</t>
-  </si>
-  <si>
-    <t>0142399347</t>
-  </si>
-  <si>
-    <t>0565552032</t>
-  </si>
-  <si>
-    <t>0501330351</t>
-  </si>
-  <si>
-    <t>0574770272</t>
-  </si>
-  <si>
-    <t>0143402446</t>
-  </si>
-  <si>
-    <t>0585665420</t>
-  </si>
-  <si>
-    <t>0152825588</t>
-  </si>
-  <si>
-    <t>0747549482</t>
-  </si>
-  <si>
-    <t>0505445280</t>
-  </si>
-  <si>
-    <t>0153690116</t>
-  </si>
-  <si>
-    <t>0152888446</t>
-  </si>
-  <si>
-    <t>0707585815</t>
-  </si>
-  <si>
-    <t>0545261916</t>
-  </si>
-  <si>
-    <t>0707393658</t>
-  </si>
-  <si>
-    <t>0712069892</t>
-  </si>
-  <si>
-    <t>0151510045</t>
-  </si>
-  <si>
-    <t>0101505574</t>
-  </si>
-  <si>
-    <t>0778190368</t>
-  </si>
-  <si>
-    <t>0556946538</t>
-  </si>
-  <si>
-    <t>0103433082</t>
-  </si>
-  <si>
-    <t>0504182722</t>
-  </si>
-  <si>
-    <t>0102513716</t>
-  </si>
-  <si>
-    <t>0748825345</t>
-  </si>
-  <si>
-    <t>0566225833</t>
-  </si>
-  <si>
-    <t>0585546020</t>
-  </si>
-  <si>
-    <t>0545382790</t>
-  </si>
-  <si>
-    <t>0151990798</t>
-  </si>
-  <si>
-    <t>0768085642</t>
-  </si>
-  <si>
-    <t>0160336649</t>
-  </si>
-  <si>
-    <t>0748288009</t>
-  </si>
-  <si>
-    <t>0704518747</t>
-  </si>
-  <si>
-    <t>0102357642</t>
-  </si>
-  <si>
-    <t>0102033985</t>
-  </si>
-  <si>
-    <t>0707763159</t>
-  </si>
-  <si>
-    <t>0757306246</t>
-  </si>
-  <si>
-    <t>0748774812</t>
-  </si>
-  <si>
-    <t>0546105095</t>
-  </si>
-  <si>
-    <t>0171825651</t>
-  </si>
-  <si>
-    <t>0151728340</t>
-  </si>
-  <si>
-    <t>0709343542</t>
-  </si>
-  <si>
-    <t>0748340816</t>
-  </si>
-  <si>
-    <t>0143244130</t>
-  </si>
-  <si>
-    <t>0749478222</t>
-  </si>
-  <si>
-    <t>0707404350</t>
-  </si>
-  <si>
-    <t>0748991868</t>
-  </si>
-  <si>
-    <t>0173747542</t>
-  </si>
-  <si>
-    <t>0100686253</t>
-  </si>
-  <si>
-    <t>0707708631</t>
-  </si>
-  <si>
-    <t>0749366633</t>
-  </si>
-  <si>
-    <t>0779345494</t>
-  </si>
-  <si>
-    <t>0506128781</t>
-  </si>
-  <si>
-    <t>0768366652</t>
-  </si>
-  <si>
-    <t>0797190764</t>
-  </si>
-  <si>
-    <t>0709123603</t>
-  </si>
-  <si>
-    <t>0555393023</t>
-  </si>
-  <si>
-    <t>0500728564</t>
-  </si>
-  <si>
-    <t>0544612143</t>
-  </si>
-  <si>
-    <t>0506041687</t>
-  </si>
-  <si>
-    <t>0778655066</t>
-  </si>
-  <si>
-    <t>0505957500</t>
-  </si>
-  <si>
-    <t>0709406256</t>
-  </si>
-  <si>
-    <t>0779260113</t>
-  </si>
-  <si>
-    <t>0545232406</t>
-  </si>
-  <si>
-    <t>0585767821</t>
-  </si>
-  <si>
-    <t>0717045033</t>
-  </si>
-  <si>
-    <t>0787665053</t>
-  </si>
-  <si>
-    <t>0151699136</t>
-  </si>
-  <si>
-    <t>0707363725</t>
-  </si>
-  <si>
-    <t>0546513733</t>
-  </si>
-  <si>
-    <t>0748876685</t>
-  </si>
-  <si>
-    <t>0707729708</t>
-  </si>
-  <si>
-    <t>0769301096</t>
-  </si>
-  <si>
-    <t>0101896378</t>
-  </si>
-  <si>
-    <t>0788281895</t>
-  </si>
-  <si>
-    <t>0707065849</t>
-  </si>
-  <si>
-    <t>0504264363</t>
-  </si>
-  <si>
-    <t>0507505142</t>
-  </si>
-  <si>
-    <t>0555520639</t>
-  </si>
-  <si>
-    <t>0717248876</t>
-  </si>
-  <si>
-    <t>0101789106</t>
-  </si>
-  <si>
-    <t>0160044848</t>
-  </si>
-  <si>
-    <t>0564941016</t>
-  </si>
-  <si>
-    <t>0576210421</t>
-  </si>
-  <si>
-    <t>0503551196</t>
-  </si>
-  <si>
-    <t>0502982110</t>
-  </si>
-  <si>
-    <t>0143117311</t>
-  </si>
-  <si>
-    <t>0707723357</t>
-  </si>
-  <si>
-    <t>0707134873</t>
-  </si>
-  <si>
-    <t>0151510002</t>
-  </si>
-  <si>
-    <t>0101473704</t>
-  </si>
-  <si>
-    <t>0555332608</t>
-  </si>
-  <si>
-    <t>0585470782</t>
-  </si>
-  <si>
-    <t>0152751536</t>
-  </si>
-  <si>
-    <t>0546228624</t>
-  </si>
-  <si>
-    <t>0585470792</t>
-  </si>
-  <si>
-    <t>0565118617</t>
-  </si>
-  <si>
-    <t>0153443580</t>
-  </si>
-  <si>
-    <t>0768084623</t>
-  </si>
-  <si>
-    <t>0171964324</t>
-  </si>
-  <si>
-    <t>0707279861</t>
-  </si>
-  <si>
-    <t>0709164466</t>
-  </si>
-  <si>
-    <t>0143214740</t>
-  </si>
-  <si>
-    <t>0709767357</t>
-  </si>
-  <si>
-    <t>0544751677</t>
-  </si>
-  <si>
-    <t>0160513433</t>
-  </si>
-  <si>
-    <t>0575873501</t>
-  </si>
-  <si>
-    <t>0596567331</t>
-  </si>
-  <si>
-    <t>0170500937</t>
-  </si>
-  <si>
-    <t>0506581600</t>
-  </si>
-  <si>
-    <t>0707562824</t>
-  </si>
-  <si>
-    <t>0708555992</t>
-  </si>
-  <si>
-    <t>0584801017</t>
-  </si>
-  <si>
-    <t>0103540242</t>
-  </si>
-  <si>
-    <t>0779259990</t>
-  </si>
-  <si>
-    <t>0711100744</t>
-  </si>
-  <si>
-    <t>0101020540</t>
-  </si>
-  <si>
-    <t>0777825384</t>
-  </si>
-  <si>
-    <t>0102667801</t>
-  </si>
-  <si>
-    <t>0555593449</t>
-  </si>
-  <si>
-    <t>0707081517</t>
-  </si>
-  <si>
-    <t>0142409066</t>
-  </si>
-  <si>
-    <t>0156561708</t>
-  </si>
-  <si>
-    <t>0142349811</t>
-  </si>
-  <si>
-    <t>0505808018</t>
-  </si>
-  <si>
-    <t>0705015315</t>
-  </si>
-  <si>
-    <t>0719574847</t>
-  </si>
-  <si>
-    <t>0565676325</t>
-  </si>
-  <si>
-    <t>0777981026</t>
-  </si>
-  <si>
-    <t>0584958829</t>
-  </si>
-  <si>
-    <t>0160533492</t>
-  </si>
-  <si>
-    <t>0749000339</t>
-  </si>
-  <si>
-    <t>0768515182</t>
-  </si>
-  <si>
-    <t>0779855094</t>
-  </si>
-  <si>
-    <t>0161911549</t>
-  </si>
-  <si>
-    <t>0767040581</t>
-  </si>
-  <si>
-    <t>0586153604</t>
-  </si>
-  <si>
-    <t>0705082537</t>
-  </si>
-  <si>
-    <t>0588634247</t>
-  </si>
-  <si>
-    <t>0787419744</t>
-  </si>
-  <si>
-    <t>0708263002</t>
-  </si>
-  <si>
-    <t>0708257533</t>
-  </si>
-  <si>
-    <t>0798995327</t>
-  </si>
-  <si>
-    <t>0749761151</t>
-  </si>
-  <si>
-    <t>0544684446</t>
-  </si>
-  <si>
-    <t>0140221850</t>
-  </si>
-  <si>
-    <t>0747716535</t>
-  </si>
-  <si>
-    <t>0708445838</t>
-  </si>
-  <si>
-    <t>0160641362</t>
-  </si>
-  <si>
-    <t>0144406638</t>
-  </si>
-  <si>
-    <t>0150900705</t>
-  </si>
-  <si>
-    <t>0500394270</t>
-  </si>
-  <si>
-    <t>0778540701</t>
-  </si>
-  <si>
-    <t>0545453886</t>
-  </si>
-  <si>
-    <t>0777089603</t>
-  </si>
-  <si>
-    <t>0142084597</t>
-  </si>
-  <si>
-    <t>0749268078</t>
-  </si>
-  <si>
-    <t>0156959680</t>
-  </si>
-  <si>
-    <t>0757350879</t>
-  </si>
-  <si>
-    <t>0172257152</t>
-  </si>
-  <si>
-    <t>0143923253</t>
-  </si>
-  <si>
-    <t>0747445549</t>
-  </si>
-  <si>
-    <t>0544239975</t>
-  </si>
-  <si>
-    <t>0173208619</t>
-  </si>
-  <si>
-    <t>0798042063</t>
-  </si>
-  <si>
-    <t>0777679647</t>
-  </si>
-  <si>
-    <t>0143946148</t>
-  </si>
-  <si>
-    <t>0585059930</t>
-  </si>
-  <si>
-    <t>0787797955</t>
-  </si>
-  <si>
-    <t>0566628344</t>
-  </si>
-  <si>
-    <t>0594970797</t>
-  </si>
-  <si>
-    <t>0151015666</t>
-  </si>
-  <si>
-    <t>0749293791</t>
-  </si>
-  <si>
-    <t>0150028676</t>
-  </si>
-  <si>
-    <t>0101267351</t>
-  </si>
-  <si>
-    <t>0171834912</t>
-  </si>
-  <si>
-    <t>0503619464</t>
-  </si>
-  <si>
-    <t>0701839686</t>
-  </si>
-  <si>
-    <t>0173934023</t>
-  </si>
-  <si>
-    <t>0152364488</t>
-  </si>
-  <si>
-    <t>0722804546</t>
-  </si>
-  <si>
-    <t>0702810482</t>
-  </si>
-  <si>
-    <t>0708926926</t>
-  </si>
-  <si>
-    <t>0767943977</t>
-  </si>
-  <si>
-    <t>0141961717</t>
-  </si>
-  <si>
-    <t>0576751644</t>
-  </si>
-  <si>
-    <t>0101408282</t>
-  </si>
-  <si>
-    <t>0709261860</t>
-  </si>
-  <si>
-    <t>0708084408</t>
-  </si>
-  <si>
-    <t>0757981206</t>
-  </si>
-  <si>
-    <t>0758875880</t>
-  </si>
-  <si>
-    <t>0504405555</t>
-  </si>
-  <si>
-    <t>0508530301</t>
-  </si>
-  <si>
-    <t>0144505829</t>
-  </si>
-  <si>
-    <t>0576354461</t>
-  </si>
-  <si>
-    <t>0150608850</t>
-  </si>
-  <si>
-    <t>0748522411</t>
-  </si>
-  <si>
-    <t>0757577132</t>
-  </si>
-  <si>
-    <t>0708302252</t>
-  </si>
-  <si>
-    <t>0585858121</t>
-  </si>
-  <si>
-    <t>0788419502</t>
-  </si>
-  <si>
-    <t>0505048539</t>
-  </si>
-  <si>
-    <t>0778461468</t>
-  </si>
-  <si>
-    <t>0152528880</t>
-  </si>
-  <si>
-    <t>0152212512</t>
-  </si>
-  <si>
-    <t>0141866570</t>
-  </si>
-  <si>
-    <t>0707442010</t>
-  </si>
-  <si>
-    <t>0152820232</t>
-  </si>
-  <si>
-    <t>0565016772</t>
-  </si>
-  <si>
-    <t>0152854158</t>
-  </si>
-  <si>
-    <t>0500658319</t>
-  </si>
-  <si>
-    <t>0713914315</t>
-  </si>
-  <si>
-    <t>0705885555</t>
-  </si>
-  <si>
-    <t>0102123827</t>
-  </si>
-  <si>
-    <t>0555980045</t>
-  </si>
-  <si>
-    <t>0158569514</t>
-  </si>
-  <si>
-    <t>0555674731</t>
-  </si>
-  <si>
-    <t>0503141520</t>
-  </si>
-  <si>
-    <t>0556135544</t>
-  </si>
-  <si>
-    <t>0564499952</t>
-  </si>
-  <si>
-    <t>0505444718</t>
-  </si>
-  <si>
-    <t>0508052455</t>
-  </si>
-  <si>
-    <t>0142859211</t>
-  </si>
-  <si>
-    <t>0101326666</t>
-  </si>
-  <si>
-    <t>0125554408</t>
-  </si>
-  <si>
-    <t>0707113939</t>
-  </si>
-  <si>
-    <t>0708181859</t>
-  </si>
-  <si>
-    <t>0707660599</t>
-  </si>
-  <si>
-    <t>0545876340</t>
-  </si>
-  <si>
-    <t>0556938613</t>
-  </si>
-  <si>
-    <t>0715152541</t>
-  </si>
-  <si>
-    <t>0718877596</t>
-  </si>
-  <si>
-    <t>0566136787</t>
-  </si>
-  <si>
-    <t>0564502321</t>
-  </si>
-  <si>
-    <t>0102730907</t>
-  </si>
-  <si>
-    <t>0769568776</t>
-  </si>
-  <si>
-    <t>0769106014</t>
-  </si>
-  <si>
-    <t>0505005491</t>
-  </si>
-  <si>
-    <t>0779020593</t>
-  </si>
-  <si>
-    <t>0707615352</t>
-  </si>
-  <si>
-    <t>0153270541</t>
-  </si>
-  <si>
-    <t>0153355182</t>
-  </si>
-  <si>
-    <t>0142085681</t>
-  </si>
-  <si>
-    <t>0757237489</t>
-  </si>
-  <si>
-    <t>0708637712</t>
-  </si>
-  <si>
-    <t>0545848633</t>
-  </si>
-  <si>
-    <t>0715578456</t>
-  </si>
-  <si>
-    <t>0787946260</t>
-  </si>
-  <si>
-    <t>0789711069</t>
-  </si>
-  <si>
-    <t>0778295499</t>
-  </si>
-  <si>
-    <t>0141452098</t>
-  </si>
-  <si>
-    <t>0757995568</t>
-  </si>
-  <si>
-    <t>0143251873</t>
-  </si>
-  <si>
-    <t>0709818381</t>
-  </si>
-  <si>
-    <t>0506916476</t>
-  </si>
-  <si>
-    <t>0747146398</t>
-  </si>
-  <si>
-    <t>0153174137</t>
-  </si>
-  <si>
-    <t>0707166403</t>
-  </si>
-  <si>
-    <t>0544200583</t>
-  </si>
-  <si>
-    <t>0708456868</t>
-  </si>
-  <si>
-    <t>0709326309</t>
-  </si>
-  <si>
-    <t>0748016426</t>
-  </si>
-  <si>
-    <t>0556297632</t>
-  </si>
-  <si>
-    <t>0142366967</t>
-  </si>
-  <si>
-    <t>0150827758</t>
-  </si>
-  <si>
-    <t>0547526336</t>
-  </si>
-  <si>
-    <t>0748539651</t>
-  </si>
-  <si>
-    <t>0789804207</t>
-  </si>
-  <si>
-    <t>0711845459</t>
-  </si>
-  <si>
-    <t>0749079876</t>
-  </si>
-  <si>
-    <t>0502420885</t>
-  </si>
-  <si>
-    <t>0503561835</t>
-  </si>
-  <si>
-    <t>0787237664</t>
-  </si>
-  <si>
-    <t>0544803606</t>
-  </si>
-  <si>
-    <t>0172080200</t>
-  </si>
-  <si>
-    <t>0707932859</t>
-  </si>
-  <si>
-    <t>0777470390</t>
-  </si>
-  <si>
-    <t>0140636475</t>
-  </si>
-  <si>
-    <t>0747923385</t>
-  </si>
-  <si>
-    <t>0757047590</t>
-  </si>
-  <si>
-    <t>0101516466</t>
-  </si>
-  <si>
-    <t>0779480000</t>
-  </si>
-  <si>
-    <t>0506795076</t>
-  </si>
-  <si>
-    <t>0564841650</t>
-  </si>
-  <si>
-    <t>0767861182</t>
-  </si>
-  <si>
-    <t>0707101767</t>
-  </si>
-  <si>
-    <t>0707671059</t>
-  </si>
-  <si>
-    <t>0560021012</t>
-  </si>
-  <si>
-    <t>0554466647</t>
-  </si>
-  <si>
-    <t>0160759241</t>
-  </si>
-  <si>
-    <t>0170008856</t>
-  </si>
-  <si>
-    <t>0711754362</t>
-  </si>
-  <si>
-    <t>0545536673</t>
-  </si>
-  <si>
-    <t>0102355807</t>
-  </si>
-  <si>
-    <t>0714331670</t>
-  </si>
-  <si>
-    <t>0708842044</t>
-  </si>
-  <si>
-    <t>0143423244</t>
-  </si>
-  <si>
-    <t>0555071595</t>
-  </si>
-  <si>
-    <t>0749057437</t>
-  </si>
-  <si>
-    <t>0102490136</t>
-  </si>
-  <si>
-    <t>0708989017</t>
-  </si>
-  <si>
-    <t>0153417242</t>
-  </si>
-  <si>
-    <t>0747128858</t>
-  </si>
-  <si>
-    <t>0707448981</t>
-  </si>
-  <si>
-    <t>0143752618</t>
-  </si>
-  <si>
-    <t>0540540525</t>
-  </si>
-  <si>
-    <t>0707552219</t>
-  </si>
-  <si>
-    <t>0507086049</t>
-  </si>
-  <si>
-    <t>0707778780</t>
-  </si>
-  <si>
-    <t>0101646680</t>
-  </si>
-  <si>
-    <t>0154541608</t>
-  </si>
-  <si>
-    <t>0107003435</t>
-  </si>
-  <si>
-    <t>0549491715</t>
-  </si>
-  <si>
-    <t>0102021418</t>
-  </si>
-  <si>
-    <t>0151524142</t>
-  </si>
-  <si>
-    <t>0544272544</t>
-  </si>
-  <si>
-    <t>0707304772</t>
-  </si>
-  <si>
-    <t>0150645021</t>
-  </si>
-  <si>
-    <t>0758247094</t>
-  </si>
-  <si>
-    <t>0779141598</t>
-  </si>
-  <si>
-    <t>0787590046</t>
-  </si>
-  <si>
-    <t>0505320121</t>
-  </si>
-  <si>
-    <t>0708964571</t>
-  </si>
-  <si>
-    <t>0505357528</t>
-  </si>
-  <si>
-    <t>0705444358</t>
-  </si>
-  <si>
-    <t>0152821414</t>
-  </si>
-  <si>
-    <t>0707468633</t>
-  </si>
-  <si>
-    <t>0118244473</t>
-  </si>
-  <si>
-    <t>0705015415</t>
-  </si>
-  <si>
-    <t>0545217995</t>
-  </si>
-  <si>
-    <t>0171992819</t>
-  </si>
-  <si>
-    <t>0140437004</t>
-  </si>
-  <si>
-    <t>0576178316</t>
-  </si>
-  <si>
-    <t>0544301963</t>
-  </si>
-  <si>
-    <t>0747089180</t>
-  </si>
-  <si>
-    <t>0501068079</t>
-  </si>
-  <si>
-    <t>0749273284</t>
-  </si>
-  <si>
-    <t>0708209108</t>
-  </si>
-  <si>
-    <t>0544113875</t>
-  </si>
-  <si>
-    <t>0507613012</t>
-  </si>
-  <si>
-    <t>0103257775</t>
-  </si>
-  <si>
-    <t>0102626346</t>
-  </si>
-  <si>
-    <t>0779595380</t>
-  </si>
-  <si>
-    <t>0758118469</t>
-  </si>
-  <si>
-    <t>0747904261</t>
-  </si>
-  <si>
-    <t>0544405582</t>
-  </si>
-  <si>
-    <t>0144491717</t>
-  </si>
-  <si>
-    <t>0171952527</t>
-  </si>
-  <si>
-    <t>0546202577</t>
-  </si>
-  <si>
-    <t>0788604235</t>
-  </si>
-  <si>
-    <t>0779750236</t>
-  </si>
-  <si>
-    <t>0757904498</t>
-  </si>
-  <si>
-    <t>0585044077</t>
-  </si>
-  <si>
-    <t>0797459540</t>
-  </si>
-  <si>
-    <t>0789134740</t>
-  </si>
-  <si>
-    <t>0173133025</t>
-  </si>
-  <si>
-    <t>0769922360</t>
-  </si>
-  <si>
-    <t>0779042853</t>
-  </si>
-  <si>
-    <t>0704266303</t>
-  </si>
-  <si>
-    <t>0769769597</t>
-  </si>
-  <si>
-    <t>0748144600</t>
-  </si>
-  <si>
-    <t>0500356045</t>
-  </si>
-  <si>
-    <t>0105262413</t>
-  </si>
-  <si>
-    <t>0152820003</t>
-  </si>
-  <si>
-    <t>0131325544</t>
-  </si>
-  <si>
-    <t>0508699344</t>
-  </si>
-  <si>
-    <t>0707797556</t>
-  </si>
-  <si>
-    <t>0143114908</t>
-  </si>
-  <si>
-    <t>0143986665</t>
-  </si>
-  <si>
-    <t>0788501422</t>
-  </si>
-  <si>
-    <t>0505753236</t>
-  </si>
-  <si>
-    <t>0767277084</t>
-  </si>
-  <si>
-    <t>0707803101</t>
-  </si>
-  <si>
-    <t>0748901701</t>
-  </si>
-  <si>
-    <t>0595125517</t>
-  </si>
-  <si>
-    <t>0708385889</t>
-  </si>
-  <si>
-    <t>0700221720</t>
-  </si>
-  <si>
-    <t>0576722516</t>
-  </si>
-  <si>
-    <t>0700528672</t>
-  </si>
-  <si>
-    <t>0140999846</t>
-  </si>
-  <si>
-    <t>0789098317</t>
-  </si>
-  <si>
-    <t>0172229425</t>
-  </si>
-  <si>
-    <t>0505449971</t>
-  </si>
-  <si>
-    <t>0505884988</t>
-  </si>
-  <si>
-    <t>0749707089</t>
-  </si>
-  <si>
-    <t>0576358473</t>
-  </si>
-  <si>
-    <t>0799644488</t>
-  </si>
-  <si>
-    <t>0103980756</t>
-  </si>
-  <si>
-    <t>0788014585</t>
-  </si>
-  <si>
-    <t>0789574066</t>
-  </si>
-  <si>
-    <t>0707144498</t>
-  </si>
-  <si>
-    <t>0140101866</t>
-  </si>
-  <si>
-    <t>0707820007</t>
-  </si>
-  <si>
-    <t>0767010416</t>
-  </si>
-  <si>
-    <t>0555504735</t>
-  </si>
-  <si>
-    <t>0566033374</t>
-  </si>
-  <si>
-    <t>0584191470</t>
-  </si>
-  <si>
-    <t>0701423449</t>
-  </si>
-  <si>
-    <t>0767750181</t>
-  </si>
-  <si>
-    <t>0160942339</t>
-  </si>
-  <si>
-    <t>0504279614</t>
-  </si>
-  <si>
-    <t>0501525653</t>
-  </si>
-  <si>
-    <t>0586506812</t>
-  </si>
-  <si>
-    <t>0798521680</t>
-  </si>
-  <si>
-    <t>0705408474</t>
-  </si>
-  <si>
-    <t>0545564020</t>
-  </si>
-  <si>
-    <t>0711754787</t>
-  </si>
-  <si>
-    <t>0716017586</t>
-  </si>
-  <si>
-    <t>0586996987</t>
-  </si>
-  <si>
-    <t>0704181883</t>
-  </si>
-  <si>
-    <t>0748847849</t>
-  </si>
-  <si>
-    <t>0748860906</t>
-  </si>
-  <si>
-    <t>0505180562</t>
-  </si>
-  <si>
-    <t>0556698184</t>
-  </si>
-  <si>
-    <t>0504900357</t>
-  </si>
-  <si>
-    <t>0506311662</t>
-  </si>
-  <si>
-    <t>0708213266</t>
-  </si>
-  <si>
-    <t>0506298995</t>
-  </si>
-  <si>
-    <t>0102226162</t>
-  </si>
-  <si>
-    <t>0566574551</t>
-  </si>
-  <si>
-    <t>0596669972</t>
-  </si>
-  <si>
-    <t>0508031865</t>
-  </si>
-  <si>
-    <t>0507579070</t>
-  </si>
-  <si>
-    <t>0705429781</t>
-  </si>
-  <si>
-    <t>0102520537</t>
-  </si>
-  <si>
-    <t>0708369428</t>
-  </si>
-  <si>
-    <t>0141090426</t>
-  </si>
-  <si>
-    <t>0554777555</t>
-  </si>
-  <si>
-    <t>0151867489</t>
-  </si>
-  <si>
-    <t>0554782792</t>
-  </si>
-  <si>
-    <t>0564726570</t>
-  </si>
-  <si>
-    <t>0142787881</t>
-  </si>
-  <si>
-    <t>0505502622</t>
-  </si>
-  <si>
-    <t>0142668613</t>
-  </si>
-  <si>
-    <t>0584208069</t>
-  </si>
-  <si>
-    <t>0758159980</t>
-  </si>
-  <si>
-    <t>0506711496</t>
-  </si>
-  <si>
-    <t>0142733049</t>
-  </si>
-  <si>
-    <t>0544107406</t>
-  </si>
-  <si>
-    <t>0505354643</t>
-  </si>
-  <si>
-    <t>0717187555</t>
-  </si>
-  <si>
-    <t>0101444416</t>
-  </si>
-  <si>
-    <t>0705448525</t>
-  </si>
-  <si>
-    <t>0105252544</t>
-  </si>
-  <si>
-    <t>0141747573</t>
-  </si>
-  <si>
-    <t>0703957602</t>
-  </si>
-  <si>
-    <t>0104446869</t>
-  </si>
-  <si>
-    <t>0504434110</t>
-  </si>
-  <si>
-    <t>0758289250</t>
-  </si>
-  <si>
-    <t>0585565036</t>
-  </si>
-  <si>
-    <t>0707426303</t>
-  </si>
-  <si>
-    <t>0141209925</t>
-  </si>
-  <si>
-    <t>0103989201</t>
-  </si>
-  <si>
-    <t>0504506396</t>
-  </si>
-  <si>
-    <t>0140423413</t>
-  </si>
-  <si>
-    <t>0747327317</t>
-  </si>
-  <si>
-    <t>0777081509</t>
-  </si>
-  <si>
-    <t>0759022933</t>
-  </si>
-  <si>
-    <t>0144175252</t>
-  </si>
-  <si>
-    <t>0102348275</t>
-  </si>
-  <si>
-    <t>0757681638</t>
-  </si>
-  <si>
-    <t>0152224906</t>
-  </si>
-  <si>
-    <t>0715936217</t>
-  </si>
-  <si>
-    <t>0502723488</t>
-  </si>
-  <si>
-    <t>0546105640</t>
-  </si>
-  <si>
-    <t>0505140414</t>
-  </si>
-  <si>
-    <t>0789471341</t>
-  </si>
-  <si>
-    <t>0566333932</t>
-  </si>
-  <si>
-    <t>0160996804</t>
-  </si>
-  <si>
-    <t>0101308463</t>
-  </si>
-  <si>
-    <t>0546105114</t>
-  </si>
-  <si>
-    <t>0160080476</t>
-  </si>
-  <si>
-    <t>0789058708</t>
-  </si>
-  <si>
-    <t>0758395665</t>
-  </si>
-  <si>
-    <t>0715398665</t>
-  </si>
-  <si>
-    <t>0674895040</t>
-  </si>
-  <si>
-    <t>0706035681</t>
-  </si>
-  <si>
-    <t>0707892929</t>
-  </si>
-  <si>
-    <t>0566696307</t>
-  </si>
-  <si>
-    <t>0505938581</t>
-  </si>
-  <si>
-    <t>0709902115</t>
-  </si>
-  <si>
-    <t>0153103448</t>
-  </si>
-  <si>
-    <t>0758203272</t>
-  </si>
-  <si>
-    <t>0787977500</t>
-  </si>
-  <si>
-    <t>0708056417</t>
-  </si>
-  <si>
-    <t>0708730755</t>
-  </si>
-  <si>
-    <t>0707472182</t>
-  </si>
-  <si>
-    <t>0584416018</t>
-  </si>
-  <si>
-    <t>0507948924</t>
-  </si>
-  <si>
-    <t>0152005247</t>
-  </si>
-  <si>
-    <t>0171686929</t>
-  </si>
-  <si>
-    <t>0708976792</t>
-  </si>
-  <si>
-    <t>0556541467</t>
-  </si>
-  <si>
-    <t>0160590174</t>
-  </si>
-  <si>
-    <t>0710014387</t>
-  </si>
-  <si>
-    <t>0711770630</t>
-  </si>
-  <si>
-    <t>0161304864</t>
-  </si>
-  <si>
-    <t>0504320429</t>
-  </si>
-  <si>
-    <t>0142404423</t>
-  </si>
-  <si>
-    <t>0545269326</t>
-  </si>
-  <si>
-    <t>0788889084</t>
-  </si>
-  <si>
-    <t>0141411407</t>
-  </si>
-  <si>
-    <t>0504291268</t>
-  </si>
-  <si>
-    <t>0709755045</t>
-  </si>
-  <si>
-    <t>0101516331</t>
-  </si>
-  <si>
-    <t>0505065016</t>
-  </si>
-  <si>
-    <t>0586623733</t>
-  </si>
-  <si>
-    <t>0778048385</t>
-  </si>
-  <si>
-    <t>0140636878</t>
-  </si>
-  <si>
-    <t>0708176165</t>
-  </si>
-  <si>
-    <t>0718343968</t>
-  </si>
-  <si>
-    <t>0153476646</t>
-  </si>
-  <si>
-    <t>0140419692</t>
-  </si>
-  <si>
-    <t>0153007822</t>
-  </si>
-  <si>
-    <t>0759192449</t>
-  </si>
-  <si>
-    <t>0749012329</t>
-  </si>
-  <si>
-    <t>0143619791</t>
-  </si>
-  <si>
-    <t>0708356524</t>
-  </si>
-  <si>
-    <t>0596102296</t>
-  </si>
-  <si>
-    <t>0503647184</t>
-  </si>
-  <si>
-    <t>0709813335</t>
-  </si>
-  <si>
-    <t>0504270466</t>
-  </si>
-  <si>
-    <t>0596108042</t>
-  </si>
-  <si>
-    <t>0707391194</t>
-  </si>
-  <si>
-    <t>0575502182</t>
-  </si>
-  <si>
-    <t>0769647653</t>
-  </si>
-  <si>
-    <t>0503391549</t>
-  </si>
-  <si>
-    <t>0505298865</t>
-  </si>
-  <si>
-    <t>0576883563</t>
-  </si>
-  <si>
-    <t>0504954511</t>
-  </si>
-  <si>
-    <t>0171402258</t>
-  </si>
-  <si>
-    <t>0505305842</t>
-  </si>
-  <si>
-    <t>0709007289</t>
-  </si>
-  <si>
-    <t>0565397414</t>
-  </si>
-  <si>
-    <t>0712520219</t>
-  </si>
-  <si>
-    <t>0141531267</t>
-  </si>
-  <si>
-    <t>0102166823</t>
-  </si>
-  <si>
-    <t>0501050852</t>
-  </si>
-  <si>
-    <t>0170585810</t>
-  </si>
-  <si>
-    <t>0585244266</t>
-  </si>
-  <si>
-    <t>0545099092</t>
-  </si>
-  <si>
-    <t>0768925338</t>
-  </si>
-  <si>
-    <t>0566160804</t>
-  </si>
-  <si>
-    <t>0505680589</t>
-  </si>
-  <si>
-    <t>0160827010</t>
-  </si>
-  <si>
-    <t>0788882699</t>
-  </si>
-  <si>
-    <t>0506955580</t>
-  </si>
-  <si>
-    <t>0142671746</t>
-  </si>
-  <si>
-    <t>0787186740</t>
-  </si>
-  <si>
-    <t>0501410753</t>
-  </si>
-  <si>
-    <t>0586965192</t>
-  </si>
-  <si>
-    <t>0153768996</t>
-  </si>
-  <si>
-    <t>0767739038</t>
-  </si>
-  <si>
-    <t>0171329793</t>
-  </si>
-  <si>
-    <t>0544560934</t>
-  </si>
-  <si>
-    <t>0706138129</t>
-  </si>
-  <si>
-    <t>0151901258</t>
-  </si>
-  <si>
-    <t>0757124146</t>
-  </si>
-  <si>
-    <t>0156723903</t>
-  </si>
-  <si>
-    <t>0720352566</t>
-  </si>
-  <si>
-    <t>0707890623</t>
-  </si>
-  <si>
-    <t>0747454866</t>
-  </si>
-  <si>
-    <t>0779476493</t>
-  </si>
-  <si>
-    <t>0709807962</t>
-  </si>
-  <si>
-    <t>0143827169</t>
-  </si>
-  <si>
-    <t>0708762325</t>
-  </si>
-  <si>
-    <t>0502278985</t>
-  </si>
-  <si>
-    <t>0170059666</t>
-  </si>
-  <si>
-    <t>0757498135</t>
-  </si>
-  <si>
-    <t>0103071057</t>
-  </si>
-  <si>
-    <t>0796696452</t>
-  </si>
-  <si>
-    <t>0784513640</t>
-  </si>
-  <si>
-    <t>0185869040</t>
-  </si>
-  <si>
-    <t>0556606100</t>
-  </si>
-  <si>
-    <t>0555825272</t>
-  </si>
-  <si>
-    <t>0102981617</t>
-  </si>
-  <si>
-    <t>0150524346</t>
-  </si>
-  <si>
-    <t>0140415253</t>
-  </si>
-  <si>
-    <t>0749137618</t>
-  </si>
-  <si>
-    <t>0502804391</t>
-  </si>
-  <si>
-    <t>0748521185</t>
-  </si>
-  <si>
-    <t>0052524443</t>
-  </si>
-  <si>
-    <t>0787887297</t>
-  </si>
-  <si>
-    <t>0142809190</t>
-  </si>
-  <si>
-    <t>0105643348</t>
-  </si>
-  <si>
-    <t>0150425884</t>
-  </si>
-  <si>
-    <t>0161604041</t>
-  </si>
-  <si>
-    <t>0708175247</t>
-  </si>
-  <si>
-    <t>0713540877</t>
-  </si>
-  <si>
-    <t>0787682604</t>
-  </si>
-  <si>
-    <t>0758028450</t>
-  </si>
-  <si>
-    <t>0779169882</t>
-  </si>
-  <si>
-    <t>0702024460</t>
-  </si>
-  <si>
-    <t>0103255143</t>
-  </si>
-  <si>
-    <t>0705026611</t>
-  </si>
-  <si>
-    <t>0797311827</t>
-  </si>
-  <si>
-    <t>0708791438</t>
-  </si>
-  <si>
-    <t>0171224051</t>
-  </si>
-  <si>
-    <t>0515456355</t>
-  </si>
-  <si>
-    <t>0789964112</t>
-  </si>
-  <si>
-    <t>0150343285</t>
-  </si>
-  <si>
-    <t>0150359320</t>
-  </si>
-  <si>
-    <t>0150375491</t>
-  </si>
-  <si>
-    <t>0555707289</t>
-  </si>
-  <si>
-    <t>0152877763</t>
-  </si>
-  <si>
-    <t>0752080944</t>
-  </si>
-  <si>
-    <t>0173471278</t>
-  </si>
-  <si>
-    <t>0769264640</t>
-  </si>
-  <si>
-    <t>0544636394</t>
-  </si>
-  <si>
-    <t>0574336118</t>
-  </si>
-  <si>
-    <t>0158800046</t>
-  </si>
-  <si>
-    <t>0769395486</t>
-  </si>
-  <si>
-    <t>0143636429</t>
-  </si>
-  <si>
-    <t>0105646480</t>
-  </si>
-  <si>
-    <t>0749541078</t>
-  </si>
-  <si>
-    <t>0566640046</t>
-  </si>
-  <si>
-    <t>0546454059</t>
-  </si>
-  <si>
-    <t>0161395079</t>
-  </si>
-  <si>
-    <t>0500335194</t>
-  </si>
-  <si>
-    <t>0160324899</t>
-  </si>
-  <si>
-    <t>0555721085</t>
-  </si>
-  <si>
-    <t>0708274679</t>
-  </si>
-  <si>
-    <t>0503672296</t>
-  </si>
-  <si>
-    <t>0595765254</t>
-  </si>
-  <si>
-    <t>0585060903</t>
-  </si>
-  <si>
-    <t>0777850516</t>
-  </si>
-  <si>
-    <t>0586097826</t>
-  </si>
-  <si>
-    <t>0554947941</t>
-  </si>
-  <si>
-    <t>0596456613</t>
-  </si>
-  <si>
-    <t>0555192367</t>
-  </si>
-  <si>
-    <t>0787882330</t>
-  </si>
-  <si>
-    <t>0707050117</t>
-  </si>
-  <si>
-    <t>0158580046</t>
-  </si>
-  <si>
-    <t>0707445512</t>
-  </si>
-  <si>
-    <t>0501552123</t>
-  </si>
-  <si>
-    <t>0107444612</t>
-  </si>
-  <si>
-    <t>0748042880</t>
-  </si>
-  <si>
-    <t>0779501991</t>
-  </si>
-  <si>
-    <t>0554762509</t>
-  </si>
-  <si>
-    <t>0100524016</t>
-  </si>
-  <si>
-    <t>0151118702</t>
-  </si>
-  <si>
-    <t>0788738955</t>
-  </si>
-  <si>
-    <t>0749593498</t>
-  </si>
-  <si>
-    <t>0747647144</t>
-  </si>
-  <si>
-    <t>0787266330</t>
-  </si>
-  <si>
-    <t>0714371221</t>
-  </si>
-  <si>
-    <t>0702881915</t>
-  </si>
-  <si>
-    <t>0749291932</t>
-  </si>
-  <si>
-    <t>0718761701</t>
-  </si>
-  <si>
-    <t>0708708017</t>
-  </si>
-  <si>
-    <t>0160618094</t>
-  </si>
-  <si>
-    <t>0768679295</t>
-  </si>
-  <si>
-    <t>0709879123</t>
-  </si>
-  <si>
-    <t>0706733590</t>
-  </si>
-  <si>
-    <t>0546487718</t>
-  </si>
-  <si>
-    <t>0595743537</t>
-  </si>
-  <si>
-    <t>0708054941</t>
-  </si>
-  <si>
-    <t>0705527431</t>
-  </si>
-  <si>
-    <t>0788246178</t>
-  </si>
-  <si>
-    <t>0104804450</t>
-  </si>
-  <si>
-    <t>0718508295</t>
-  </si>
-  <si>
-    <t>0707687007</t>
-  </si>
-  <si>
-    <t>0759275516</t>
-  </si>
-  <si>
-    <t>0707331327</t>
-  </si>
-  <si>
-    <t>0501787276</t>
-  </si>
-  <si>
-    <t>0140974202</t>
-  </si>
-  <si>
-    <t>0709127118</t>
-  </si>
-  <si>
-    <t>0707771590</t>
-  </si>
-  <si>
-    <t>0708822405</t>
-  </si>
-  <si>
-    <t>0140095191</t>
-  </si>
-  <si>
-    <t>0707829129</t>
-  </si>
-  <si>
-    <t>0152157410</t>
-  </si>
-  <si>
-    <t>0757346565</t>
-  </si>
-  <si>
-    <t>0508024496</t>
-  </si>
-  <si>
-    <t>0152858244</t>
-  </si>
-  <si>
-    <t>0704526052</t>
-  </si>
-  <si>
-    <t>0748731208</t>
-  </si>
-  <si>
-    <t>0574061065</t>
-  </si>
-  <si>
-    <t>0506414601</t>
-  </si>
-  <si>
-    <t>0546703176</t>
-  </si>
-  <si>
-    <t>0777075999</t>
-  </si>
-  <si>
-    <t>0574457063</t>
-  </si>
-  <si>
-    <t>0705245519</t>
-  </si>
-  <si>
-    <t>0759550356</t>
-  </si>
-  <si>
-    <t>0584168272</t>
-  </si>
-  <si>
-    <t>0565101838</t>
-  </si>
-  <si>
-    <t>0789513630</t>
-  </si>
-  <si>
-    <t>0709095586</t>
-  </si>
-  <si>
-    <t>0544357240</t>
-  </si>
-  <si>
-    <t>0180582534</t>
-  </si>
-  <si>
-    <t>0102944350</t>
-  </si>
-  <si>
-    <t>0767776709</t>
-  </si>
-  <si>
-    <t>0575283613</t>
-  </si>
-  <si>
-    <t>0555847266</t>
-  </si>
-  <si>
-    <t>0797108101</t>
-  </si>
-  <si>
-    <t>0566820153</t>
-  </si>
-  <si>
-    <t>0143552705</t>
-  </si>
-  <si>
-    <t>0152286105</t>
-  </si>
-  <si>
-    <t>0164645359</t>
-  </si>
-  <si>
-    <t>0101706202</t>
-  </si>
-  <si>
-    <t>0172125633</t>
-  </si>
-  <si>
-    <t>0749676307</t>
-  </si>
-  <si>
-    <t>0155668088</t>
-  </si>
-  <si>
-    <t>0566521271</t>
-  </si>
-  <si>
-    <t>0768838170</t>
-  </si>
-  <si>
-    <t>0789496648</t>
-  </si>
-  <si>
-    <t>0544924177</t>
-  </si>
-  <si>
-    <t>0789209093</t>
-  </si>
-  <si>
-    <t>0574390409</t>
-  </si>
-  <si>
-    <t>0704538793</t>
-  </si>
-  <si>
-    <t>0576644255</t>
-  </si>
-  <si>
-    <t>0757832821</t>
-  </si>
-  <si>
-    <t>0757061026</t>
-  </si>
-  <si>
-    <t>0777327269</t>
-  </si>
-  <si>
-    <t>0594841671</t>
-  </si>
-  <si>
-    <t>0777835240</t>
-  </si>
-  <si>
-    <t>0152296606</t>
-  </si>
-  <si>
-    <t>0503768718</t>
-  </si>
-  <si>
-    <t>0759901504</t>
-  </si>
-  <si>
-    <t>0101290309</t>
-  </si>
-  <si>
-    <t>0787398327</t>
-  </si>
-  <si>
-    <t>0768240111</t>
-  </si>
-  <si>
-    <t>0502805734</t>
-  </si>
-  <si>
-    <t>0152518904</t>
-  </si>
-  <si>
-    <t>0769270718</t>
-  </si>
-  <si>
-    <t>0565624892</t>
-  </si>
-  <si>
-    <t>0596788922</t>
-  </si>
-  <si>
-    <t>0142854877</t>
-  </si>
-  <si>
-    <t>0716624052</t>
-  </si>
-  <si>
-    <t>0544008778</t>
-  </si>
-  <si>
-    <t>0797691607</t>
-  </si>
-  <si>
-    <t>0757323541</t>
-  </si>
-  <si>
-    <t>0777123735</t>
-  </si>
-  <si>
-    <t>0788541480</t>
-  </si>
-  <si>
-    <t>0768953383</t>
-  </si>
-  <si>
-    <t>0787037833</t>
-  </si>
-  <si>
-    <t>0711962550</t>
-  </si>
-  <si>
-    <t>0544379794</t>
-  </si>
-  <si>
-    <t>0758654865</t>
-  </si>
-  <si>
-    <t>0788948342</t>
-  </si>
-  <si>
-    <t>0555233404</t>
-  </si>
-  <si>
-    <t>0564787971</t>
-  </si>
-  <si>
-    <t>0564619478</t>
-  </si>
-  <si>
-    <t>0706958567</t>
-  </si>
-  <si>
-    <t>0767060032</t>
-  </si>
-  <si>
-    <t>0702065060</t>
-  </si>
-  <si>
-    <t>0141968080</t>
-  </si>
-  <si>
-    <t>0767203062</t>
-  </si>
-  <si>
-    <t>0103279952</t>
-  </si>
-  <si>
-    <t>0595575373</t>
-  </si>
-  <si>
-    <t>0152410184</t>
-  </si>
-  <si>
-    <t>0142939970</t>
-  </si>
-  <si>
-    <t>0170276066</t>
-  </si>
-  <si>
-    <t>0715788341</t>
-  </si>
-  <si>
-    <t>0585791169</t>
-  </si>
-  <si>
-    <t>0759158067</t>
-  </si>
-  <si>
-    <t>0596910363</t>
-  </si>
-  <si>
-    <t>0584131164</t>
-  </si>
-  <si>
-    <t>0502209789</t>
-  </si>
-  <si>
-    <t>0103090620</t>
-  </si>
-  <si>
-    <t>0767784424</t>
-  </si>
-  <si>
-    <t>0596257398</t>
-  </si>
-  <si>
-    <t>0711359029</t>
-  </si>
-  <si>
-    <t>0545140708</t>
-  </si>
-  <si>
-    <t>0788622658</t>
-  </si>
-  <si>
-    <t>0711460247</t>
-  </si>
-  <si>
-    <t>0502960004</t>
-  </si>
-  <si>
-    <t>0545875039</t>
-  </si>
-  <si>
-    <t>0502859815</t>
-  </si>
-  <si>
-    <t>0555046622</t>
-  </si>
-  <si>
-    <t>0787699706</t>
-  </si>
-  <si>
-    <t>0708534055</t>
-  </si>
-  <si>
-    <t>0720705122</t>
-  </si>
-  <si>
-    <t>0768449097</t>
-  </si>
-  <si>
-    <t>0712789428</t>
-  </si>
-  <si>
-    <t>0798168791</t>
-  </si>
-  <si>
-    <t>0595322093</t>
-  </si>
-  <si>
-    <t>0586889693</t>
-  </si>
-  <si>
-    <t>0104045582</t>
-  </si>
-  <si>
-    <t>0707280799</t>
-  </si>
-  <si>
-    <t>0505015566</t>
-  </si>
-  <si>
-    <t>0564423126</t>
-  </si>
-  <si>
-    <t>0797702700</t>
-  </si>
-  <si>
-    <t>0101454512</t>
-  </si>
-  <si>
-    <t>0505609696</t>
-  </si>
-  <si>
-    <t>0101247791</t>
-  </si>
-  <si>
-    <t>0777249964</t>
-  </si>
-  <si>
-    <t>0565784231</t>
-  </si>
-  <si>
-    <t>0556646392</t>
-  </si>
-  <si>
-    <t>0584077365</t>
-  </si>
-  <si>
-    <t>0778783911</t>
-  </si>
-  <si>
-    <t>0787600024</t>
-  </si>
-  <si>
-    <t>0749313078</t>
-  </si>
-  <si>
-    <t>0703318647</t>
-  </si>
-  <si>
-    <t>0797686233</t>
-  </si>
-  <si>
-    <t>0555512374</t>
-  </si>
-  <si>
-    <t>0507378795</t>
-  </si>
-  <si>
-    <t>0566967477</t>
-  </si>
-  <si>
-    <t>0584959120</t>
-  </si>
-  <si>
-    <t>0504300642</t>
-  </si>
-  <si>
-    <t>0595619599</t>
-  </si>
-  <si>
-    <t>0173960626</t>
-  </si>
-  <si>
-    <t>0151383541</t>
-  </si>
-  <si>
-    <t>0555913421</t>
-  </si>
-  <si>
-    <t>0748868635</t>
-  </si>
-  <si>
-    <t>0594830423</t>
-  </si>
-  <si>
-    <t>0505548489</t>
-  </si>
-  <si>
-    <t>0585602525</t>
-  </si>
-  <si>
-    <t>0788753542</t>
-  </si>
-  <si>
-    <t>0171747461</t>
-  </si>
-  <si>
-    <t>0566106316</t>
-  </si>
-  <si>
-    <t>0767189881</t>
-  </si>
-  <si>
-    <t>0779475774</t>
-  </si>
-  <si>
-    <t>0585392957</t>
-  </si>
-  <si>
-    <t>0575274913</t>
-  </si>
-  <si>
-    <t>0749011875</t>
-  </si>
-  <si>
-    <t>0779237336</t>
-  </si>
-  <si>
-    <t>0574435082</t>
-  </si>
-  <si>
-    <t>0101687469</t>
-  </si>
-  <si>
-    <t>0701487439</t>
-  </si>
-  <si>
-    <t>0758610459</t>
-  </si>
-  <si>
-    <t>0555160381</t>
-  </si>
-  <si>
-    <t>0709303120</t>
-  </si>
-  <si>
-    <t>0125869235</t>
-  </si>
-  <si>
-    <t>0155121236</t>
-  </si>
-  <si>
-    <t>0070505446</t>
-  </si>
-  <si>
-    <t>0744405296</t>
-  </si>
-  <si>
-    <t>0194435508</t>
-  </si>
-  <si>
-    <t>0140508713</t>
-  </si>
-  <si>
-    <t>0705026464</t>
-  </si>
-  <si>
-    <t>0556462410</t>
-  </si>
-  <si>
-    <t>0707906655</t>
-  </si>
-  <si>
-    <t>0529472103</t>
-  </si>
-  <si>
-    <t>0106642854</t>
-  </si>
-  <si>
-    <t>0788980690</t>
-  </si>
-  <si>
-    <t>0778555549</t>
-  </si>
-  <si>
-    <t>0151506362</t>
-  </si>
-  <si>
-    <t>0140194085</t>
-  </si>
-  <si>
-    <t>0552844108</t>
-  </si>
-  <si>
-    <t>0506482029</t>
-  </si>
-  <si>
-    <t>0787617297</t>
-  </si>
-  <si>
-    <t>0160828255</t>
-  </si>
-  <si>
-    <t>0594706486</t>
-  </si>
-  <si>
-    <t>0102122414</t>
-  </si>
-  <si>
-    <t>0708345602</t>
-  </si>
-  <si>
-    <t>0758201607</t>
-  </si>
-  <si>
-    <t>0709361478</t>
-  </si>
-  <si>
-    <t>0506613483</t>
-  </si>
-  <si>
-    <t>0709084664</t>
-  </si>
-  <si>
-    <t>0501172768</t>
-  </si>
-  <si>
-    <t>0768799777</t>
-  </si>
-  <si>
-    <t>0711932631</t>
-  </si>
-  <si>
-    <t>0777086918</t>
-  </si>
-  <si>
-    <t>0140220974</t>
-  </si>
-  <si>
-    <t>0759595567</t>
-  </si>
-  <si>
-    <t>0747585035</t>
-  </si>
-  <si>
-    <t>0747412695</t>
-  </si>
-  <si>
-    <t>0757201996</t>
-  </si>
-  <si>
-    <t>0739069317</t>
-  </si>
-  <si>
-    <t>0554174165</t>
-  </si>
-  <si>
-    <t>0540982315</t>
-  </si>
-  <si>
-    <t>0505049984</t>
-  </si>
-  <si>
-    <t>0584156483</t>
-  </si>
-  <si>
-    <t>0574166660</t>
-  </si>
-  <si>
-    <t>0500912461</t>
-  </si>
-  <si>
-    <t>0707990047</t>
-  </si>
-  <si>
-    <t>0554632476</t>
-  </si>
-  <si>
-    <t>0160071162</t>
-  </si>
-  <si>
-    <t>0102908665</t>
-  </si>
-  <si>
-    <t>0711661622</t>
-  </si>
-  <si>
-    <t>0779883605</t>
-  </si>
-  <si>
-    <t>0758953799</t>
-  </si>
-  <si>
-    <t>0565598437</t>
-  </si>
-  <si>
-    <t>0719799275</t>
-  </si>
-  <si>
-    <t>0707824268</t>
-  </si>
-  <si>
-    <t>0153481815</t>
-  </si>
-  <si>
-    <t>0101782697</t>
-  </si>
-  <si>
-    <t>0575631273</t>
-  </si>
-  <si>
-    <t>0160236285</t>
-  </si>
-  <si>
-    <t>0176356365</t>
+    <t>225747501292</t>
+  </si>
+  <si>
+    <t>225171623293</t>
+  </si>
+  <si>
+    <t>225574257526</t>
+  </si>
+  <si>
+    <t>225748053488</t>
+  </si>
+  <si>
+    <t>225749650291</t>
+  </si>
+  <si>
+    <t>225757736220</t>
+  </si>
+  <si>
+    <t>225505528100</t>
+  </si>
+  <si>
+    <t>225594312080</t>
+  </si>
+  <si>
+    <t>225768831251</t>
+  </si>
+  <si>
+    <t>225789065217</t>
+  </si>
+  <si>
+    <t>225173795629</t>
+  </si>
+  <si>
+    <t>225749898829</t>
+  </si>
+  <si>
+    <t>225564470561</t>
+  </si>
+  <si>
+    <t>225768648490</t>
+  </si>
+  <si>
+    <t>225707147940</t>
+  </si>
+  <si>
+    <t>225101575945</t>
+  </si>
+  <si>
+    <t>225708376302</t>
+  </si>
+  <si>
+    <t>225749865878</t>
+  </si>
+  <si>
+    <t>225778121588</t>
+  </si>
+  <si>
+    <t>225707944855</t>
+  </si>
+  <si>
+    <t>225709684114</t>
+  </si>
+  <si>
+    <t>225564096117</t>
+  </si>
+  <si>
+    <t>225758452997</t>
+  </si>
+  <si>
+    <t>225586509726</t>
+  </si>
+  <si>
+    <t>225769953840</t>
+  </si>
+  <si>
+    <t>225500414954</t>
+  </si>
+  <si>
+    <t>225707983480</t>
+  </si>
+  <si>
+    <t>225574482448</t>
+  </si>
+  <si>
+    <t>225584414022</t>
+  </si>
+  <si>
+    <t>225777439564</t>
+  </si>
+  <si>
+    <t>225707378488</t>
+  </si>
+  <si>
+    <t>225141848565</t>
+  </si>
+  <si>
+    <t>225151268895</t>
+  </si>
+  <si>
+    <t>225566457094</t>
+  </si>
+  <si>
+    <t>225140033847</t>
+  </si>
+  <si>
+    <t>225778210170</t>
+  </si>
+  <si>
+    <t>225142646573</t>
+  </si>
+  <si>
+    <t>225767536232</t>
+  </si>
+  <si>
+    <t>225508094980</t>
+  </si>
+  <si>
+    <t>225574871112</t>
+  </si>
+  <si>
+    <t>225565666283</t>
+  </si>
+  <si>
+    <t>225502413232</t>
+  </si>
+  <si>
+    <t>225172469131</t>
+  </si>
+  <si>
+    <t>225749000710</t>
+  </si>
+  <si>
+    <t>225505758786</t>
+  </si>
+  <si>
+    <t>225779670355</t>
+  </si>
+  <si>
+    <t>225747224512</t>
+  </si>
+  <si>
+    <t>225707586063</t>
+  </si>
+  <si>
+    <t>225545544134</t>
+  </si>
+  <si>
+    <t>225172713139</t>
+  </si>
+  <si>
+    <t>225143398350</t>
+  </si>
+  <si>
+    <t>225748445483</t>
+  </si>
+  <si>
+    <t>225779977958</t>
+  </si>
+  <si>
+    <t>225778929075</t>
+  </si>
+  <si>
+    <t>225711332409</t>
+  </si>
+  <si>
+    <t>225103259819</t>
+  </si>
+  <si>
+    <t>225101102470</t>
+  </si>
+  <si>
+    <t>225566841064</t>
+  </si>
+  <si>
+    <t>225749977282</t>
+  </si>
+  <si>
+    <t>225555581075</t>
+  </si>
+  <si>
+    <t>225152511343</t>
+  </si>
+  <si>
+    <t>225545634573</t>
+  </si>
+  <si>
+    <t>225789189652</t>
+  </si>
+  <si>
+    <t>225500907034</t>
+  </si>
+  <si>
+    <t>225153987643</t>
+  </si>
+  <si>
+    <t>225701424647</t>
+  </si>
+  <si>
+    <t>225150114233</t>
+  </si>
+  <si>
+    <t>225709924799</t>
+  </si>
+  <si>
+    <t>225700745166</t>
+  </si>
+  <si>
+    <t>225707128162</t>
+  </si>
+  <si>
+    <t>225584498648</t>
+  </si>
+  <si>
+    <t>225101507730</t>
+  </si>
+  <si>
+    <t>225701067410</t>
+  </si>
+  <si>
+    <t>225586323416</t>
+  </si>
+  <si>
+    <t>225141143692</t>
+  </si>
+  <si>
+    <t>225747021382</t>
+  </si>
+  <si>
+    <t>225787259766</t>
+  </si>
+  <si>
+    <t>225707639734</t>
+  </si>
+  <si>
+    <t>225142636781</t>
+  </si>
+  <si>
+    <t>225500218552</t>
+  </si>
+  <si>
+    <t>225748594228</t>
+  </si>
+  <si>
+    <t>225564338638</t>
+  </si>
+  <si>
+    <t>225566409361</t>
+  </si>
+  <si>
+    <t>225103292948</t>
+  </si>
+  <si>
+    <t>225505415505</t>
+  </si>
+  <si>
+    <t>225153646408</t>
+  </si>
+  <si>
+    <t>225707681513</t>
+  </si>
+  <si>
+    <t>2259748646186</t>
+  </si>
+  <si>
+    <t>225777921724</t>
+  </si>
+  <si>
+    <t>225545488613</t>
+  </si>
+  <si>
+    <t>225152698760</t>
+  </si>
+  <si>
+    <t>225779645888</t>
+  </si>
+  <si>
+    <t>225708166834</t>
+  </si>
+  <si>
+    <t>225505979178</t>
+  </si>
+  <si>
+    <t>225707594181</t>
+  </si>
+  <si>
+    <t>225706143270</t>
+  </si>
+  <si>
+    <t>225544144174</t>
+  </si>
+  <si>
+    <t>225141035390</t>
+  </si>
+  <si>
+    <t>225748636067</t>
+  </si>
+  <si>
+    <t>225769364117</t>
+  </si>
+  <si>
+    <t>225711679753</t>
+  </si>
+  <si>
+    <t>225707686641</t>
+  </si>
+  <si>
+    <t>225140642969</t>
+  </si>
+  <si>
+    <t>225596933916</t>
+  </si>
+  <si>
+    <t>225152174685</t>
+  </si>
+  <si>
+    <t>225708927249</t>
+  </si>
+  <si>
+    <t>225101209890</t>
+  </si>
+  <si>
+    <t>225501646376</t>
+  </si>
+  <si>
+    <t>225502292075</t>
+  </si>
+  <si>
+    <t>225101664781</t>
+  </si>
+  <si>
+    <t>225594443529</t>
+  </si>
+  <si>
+    <t>225777790519</t>
+  </si>
+  <si>
+    <t>225506042025</t>
+  </si>
+  <si>
+    <t>225703615622</t>
+  </si>
+  <si>
+    <t>225152850005</t>
+  </si>
+  <si>
+    <t>225152822005</t>
+  </si>
+  <si>
+    <t>225706745019</t>
+  </si>
+  <si>
+    <t>225505554400</t>
+  </si>
+  <si>
+    <t>225709422480</t>
+  </si>
+  <si>
+    <t>225152025588</t>
+  </si>
+  <si>
+    <t>225742825063</t>
+  </si>
+  <si>
+    <t>225555400003</t>
+  </si>
+  <si>
+    <t>225758668459</t>
+  </si>
+  <si>
+    <t>225150477395</t>
+  </si>
+  <si>
+    <t>225555427751</t>
+  </si>
+  <si>
+    <t>225170582235</t>
+  </si>
+  <si>
+    <t>225779518545</t>
+  </si>
+  <si>
+    <t>225103222651</t>
+  </si>
+  <si>
+    <t>225171617026</t>
+  </si>
+  <si>
+    <t>225707843211</t>
+  </si>
+  <si>
+    <t>225505164901</t>
+  </si>
+  <si>
+    <t>225709892302</t>
+  </si>
+  <si>
+    <t>225505460863</t>
+  </si>
+  <si>
+    <t>225171643022</t>
+  </si>
+  <si>
+    <t>225707271248</t>
+  </si>
+  <si>
+    <t>225594880003</t>
+  </si>
+  <si>
+    <t>225565570588</t>
+  </si>
+  <si>
+    <t>225585772294</t>
+  </si>
+  <si>
+    <t>225788260914</t>
+  </si>
+  <si>
+    <t>225707282600</t>
+  </si>
+  <si>
+    <t>225101005588</t>
+  </si>
+  <si>
+    <t>225505224885</t>
+  </si>
+  <si>
+    <t>225150183926</t>
+  </si>
+  <si>
+    <t>225708344033</t>
+  </si>
+  <si>
+    <t>225142399347</t>
+  </si>
+  <si>
+    <t>225565552032</t>
+  </si>
+  <si>
+    <t>225501330351</t>
+  </si>
+  <si>
+    <t>225574770272</t>
+  </si>
+  <si>
+    <t>225143402446</t>
+  </si>
+  <si>
+    <t>225585665420</t>
+  </si>
+  <si>
+    <t>225152825588</t>
+  </si>
+  <si>
+    <t>225747549482</t>
+  </si>
+  <si>
+    <t>225505445280</t>
+  </si>
+  <si>
+    <t>225153690116</t>
+  </si>
+  <si>
+    <t>225152888446</t>
+  </si>
+  <si>
+    <t>225707585815</t>
+  </si>
+  <si>
+    <t>225545261916</t>
+  </si>
+  <si>
+    <t>225707393658</t>
+  </si>
+  <si>
+    <t>225712069892</t>
+  </si>
+  <si>
+    <t>225151510045</t>
+  </si>
+  <si>
+    <t>225101505574</t>
+  </si>
+  <si>
+    <t>225778190368</t>
+  </si>
+  <si>
+    <t>225556946538</t>
+  </si>
+  <si>
+    <t>225103433082</t>
+  </si>
+  <si>
+    <t>225504182722</t>
+  </si>
+  <si>
+    <t>225102513716</t>
+  </si>
+  <si>
+    <t>225748825345</t>
+  </si>
+  <si>
+    <t>225566225833</t>
+  </si>
+  <si>
+    <t>225585546020</t>
+  </si>
+  <si>
+    <t>225545382790</t>
+  </si>
+  <si>
+    <t>225151990798</t>
+  </si>
+  <si>
+    <t>225768085642</t>
+  </si>
+  <si>
+    <t>225160336649</t>
+  </si>
+  <si>
+    <t>225748288009</t>
+  </si>
+  <si>
+    <t>225704518747</t>
+  </si>
+  <si>
+    <t>225102357642</t>
+  </si>
+  <si>
+    <t>225102033985</t>
+  </si>
+  <si>
+    <t>225707763159</t>
+  </si>
+  <si>
+    <t>225757306246</t>
+  </si>
+  <si>
+    <t>225748774812</t>
+  </si>
+  <si>
+    <t>225546105095</t>
+  </si>
+  <si>
+    <t>225171825651</t>
+  </si>
+  <si>
+    <t>225151728340</t>
+  </si>
+  <si>
+    <t>225709343542</t>
+  </si>
+  <si>
+    <t>225748340816</t>
+  </si>
+  <si>
+    <t>225143244130</t>
+  </si>
+  <si>
+    <t>225749478222</t>
+  </si>
+  <si>
+    <t>225707404350</t>
+  </si>
+  <si>
+    <t>225748991868</t>
+  </si>
+  <si>
+    <t>225173747542</t>
+  </si>
+  <si>
+    <t>225100686253</t>
+  </si>
+  <si>
+    <t>225707708631</t>
+  </si>
+  <si>
+    <t>225749366633</t>
+  </si>
+  <si>
+    <t>225779345494</t>
+  </si>
+  <si>
+    <t>225506128781</t>
+  </si>
+  <si>
+    <t>225768366652</t>
+  </si>
+  <si>
+    <t>225797190764</t>
+  </si>
+  <si>
+    <t>225709123603</t>
+  </si>
+  <si>
+    <t>225555393023</t>
+  </si>
+  <si>
+    <t>225500728564</t>
+  </si>
+  <si>
+    <t>225544612143</t>
+  </si>
+  <si>
+    <t>225506041687</t>
+  </si>
+  <si>
+    <t>225778655066</t>
+  </si>
+  <si>
+    <t>225505957500</t>
+  </si>
+  <si>
+    <t>225709406256</t>
+  </si>
+  <si>
+    <t>225779260113</t>
+  </si>
+  <si>
+    <t>225545232406</t>
+  </si>
+  <si>
+    <t>225585767821</t>
+  </si>
+  <si>
+    <t>225717045033</t>
+  </si>
+  <si>
+    <t>225787665053</t>
+  </si>
+  <si>
+    <t>225151699136</t>
+  </si>
+  <si>
+    <t>225707363725</t>
+  </si>
+  <si>
+    <t>225546513733</t>
+  </si>
+  <si>
+    <t>225748876685</t>
+  </si>
+  <si>
+    <t>225707729708</t>
+  </si>
+  <si>
+    <t>225769301096</t>
+  </si>
+  <si>
+    <t>225101896378</t>
+  </si>
+  <si>
+    <t>225788281895</t>
+  </si>
+  <si>
+    <t>225707065849</t>
+  </si>
+  <si>
+    <t>225504264363</t>
+  </si>
+  <si>
+    <t>225507505142</t>
+  </si>
+  <si>
+    <t>225555520639</t>
+  </si>
+  <si>
+    <t>225717248876</t>
+  </si>
+  <si>
+    <t>225101789106</t>
+  </si>
+  <si>
+    <t>225160044848</t>
+  </si>
+  <si>
+    <t>225564941016</t>
+  </si>
+  <si>
+    <t>225576210421</t>
+  </si>
+  <si>
+    <t>225503551196</t>
+  </si>
+  <si>
+    <t>225502982110</t>
+  </si>
+  <si>
+    <t>225143117311</t>
+  </si>
+  <si>
+    <t>225707723357</t>
+  </si>
+  <si>
+    <t>225707134873</t>
+  </si>
+  <si>
+    <t>225151510002</t>
+  </si>
+  <si>
+    <t>225101473704</t>
+  </si>
+  <si>
+    <t>225555332608</t>
+  </si>
+  <si>
+    <t>225585470782</t>
+  </si>
+  <si>
+    <t>225152751536</t>
+  </si>
+  <si>
+    <t>225546228624</t>
+  </si>
+  <si>
+    <t>225585470792</t>
+  </si>
+  <si>
+    <t>225565118617</t>
+  </si>
+  <si>
+    <t>225153443580</t>
+  </si>
+  <si>
+    <t>225768084623</t>
+  </si>
+  <si>
+    <t>225171964324</t>
+  </si>
+  <si>
+    <t>225707279861</t>
+  </si>
+  <si>
+    <t>225709164466</t>
+  </si>
+  <si>
+    <t>225143214740</t>
+  </si>
+  <si>
+    <t>225709767357</t>
+  </si>
+  <si>
+    <t>225544751677</t>
+  </si>
+  <si>
+    <t>225160513433</t>
+  </si>
+  <si>
+    <t>225575873501</t>
+  </si>
+  <si>
+    <t>225596567331</t>
+  </si>
+  <si>
+    <t>225170500937</t>
+  </si>
+  <si>
+    <t>225506581600</t>
+  </si>
+  <si>
+    <t>225707562824</t>
+  </si>
+  <si>
+    <t>225708555992</t>
+  </si>
+  <si>
+    <t>225584801017</t>
+  </si>
+  <si>
+    <t>225103540242</t>
+  </si>
+  <si>
+    <t>225779259990</t>
+  </si>
+  <si>
+    <t>225711100744</t>
+  </si>
+  <si>
+    <t>225101020540</t>
+  </si>
+  <si>
+    <t>225777825384</t>
+  </si>
+  <si>
+    <t>225102667801</t>
+  </si>
+  <si>
+    <t>225555593449</t>
+  </si>
+  <si>
+    <t>225707081517</t>
+  </si>
+  <si>
+    <t>225142409066</t>
+  </si>
+  <si>
+    <t>225156561708</t>
+  </si>
+  <si>
+    <t>225142349811</t>
+  </si>
+  <si>
+    <t>225505808018</t>
+  </si>
+  <si>
+    <t>225705015315</t>
+  </si>
+  <si>
+    <t>225719574847</t>
+  </si>
+  <si>
+    <t>225565676325</t>
+  </si>
+  <si>
+    <t>225777981026</t>
+  </si>
+  <si>
+    <t>225584958829</t>
+  </si>
+  <si>
+    <t>225160533492</t>
+  </si>
+  <si>
+    <t>225749000339</t>
+  </si>
+  <si>
+    <t>225768515182</t>
+  </si>
+  <si>
+    <t>225779855094</t>
+  </si>
+  <si>
+    <t>225161911549</t>
+  </si>
+  <si>
+    <t>225767040581</t>
+  </si>
+  <si>
+    <t>225586153604</t>
+  </si>
+  <si>
+    <t>225705082537</t>
+  </si>
+  <si>
+    <t>225588634247</t>
+  </si>
+  <si>
+    <t>225787419744</t>
+  </si>
+  <si>
+    <t>225708263002</t>
+  </si>
+  <si>
+    <t>225708257533</t>
+  </si>
+  <si>
+    <t>225798995327</t>
+  </si>
+  <si>
+    <t>225749761151</t>
+  </si>
+  <si>
+    <t>225544684446</t>
+  </si>
+  <si>
+    <t>225140221850</t>
+  </si>
+  <si>
+    <t>225747716535</t>
+  </si>
+  <si>
+    <t>225708445838</t>
+  </si>
+  <si>
+    <t>225160641362</t>
+  </si>
+  <si>
+    <t>225144406638</t>
+  </si>
+  <si>
+    <t>225150900705</t>
+  </si>
+  <si>
+    <t>225500394270</t>
+  </si>
+  <si>
+    <t>225778540701</t>
+  </si>
+  <si>
+    <t>225545453886</t>
+  </si>
+  <si>
+    <t>225777089603</t>
+  </si>
+  <si>
+    <t>225142084597</t>
+  </si>
+  <si>
+    <t>225749268078</t>
+  </si>
+  <si>
+    <t>225156959680</t>
+  </si>
+  <si>
+    <t>225757350879</t>
+  </si>
+  <si>
+    <t>225172257152</t>
+  </si>
+  <si>
+    <t>225143923253</t>
+  </si>
+  <si>
+    <t>225747445549</t>
+  </si>
+  <si>
+    <t>225544239975</t>
+  </si>
+  <si>
+    <t>225173208619</t>
+  </si>
+  <si>
+    <t>225798042063</t>
+  </si>
+  <si>
+    <t>225777679647</t>
+  </si>
+  <si>
+    <t>225143946148</t>
+  </si>
+  <si>
+    <t>225585059930</t>
+  </si>
+  <si>
+    <t>225787797955</t>
+  </si>
+  <si>
+    <t>225566628344</t>
+  </si>
+  <si>
+    <t>225594970797</t>
+  </si>
+  <si>
+    <t>225151015666</t>
+  </si>
+  <si>
+    <t>225749293791</t>
+  </si>
+  <si>
+    <t>225150028676</t>
+  </si>
+  <si>
+    <t>225101267351</t>
+  </si>
+  <si>
+    <t>225171834912</t>
+  </si>
+  <si>
+    <t>225503619464</t>
+  </si>
+  <si>
+    <t>225701839686</t>
+  </si>
+  <si>
+    <t>225173934023</t>
+  </si>
+  <si>
+    <t>225152364488</t>
+  </si>
+  <si>
+    <t>225722804546</t>
+  </si>
+  <si>
+    <t>225702810482</t>
+  </si>
+  <si>
+    <t>225708926926</t>
+  </si>
+  <si>
+    <t>225767943977</t>
+  </si>
+  <si>
+    <t>225141961717</t>
+  </si>
+  <si>
+    <t>225576751644</t>
+  </si>
+  <si>
+    <t>225101408282</t>
+  </si>
+  <si>
+    <t>225709261860</t>
+  </si>
+  <si>
+    <t>225708084408</t>
+  </si>
+  <si>
+    <t>225757981206</t>
+  </si>
+  <si>
+    <t>225758875880</t>
+  </si>
+  <si>
+    <t>225504405555</t>
+  </si>
+  <si>
+    <t>225508530301</t>
+  </si>
+  <si>
+    <t>225144505829</t>
+  </si>
+  <si>
+    <t>225576354461</t>
+  </si>
+  <si>
+    <t>225150608850</t>
+  </si>
+  <si>
+    <t>225748522411</t>
+  </si>
+  <si>
+    <t>225757577132</t>
+  </si>
+  <si>
+    <t>225708302252</t>
+  </si>
+  <si>
+    <t>225585858121</t>
+  </si>
+  <si>
+    <t>225788419502</t>
+  </si>
+  <si>
+    <t>225505048539</t>
+  </si>
+  <si>
+    <t>225778461468</t>
+  </si>
+  <si>
+    <t>225152528880</t>
+  </si>
+  <si>
+    <t>225152212512</t>
+  </si>
+  <si>
+    <t>225141866570</t>
+  </si>
+  <si>
+    <t>225707442010</t>
+  </si>
+  <si>
+    <t>225152820232</t>
+  </si>
+  <si>
+    <t>225565016772</t>
+  </si>
+  <si>
+    <t>225152854158</t>
+  </si>
+  <si>
+    <t>225500658319</t>
+  </si>
+  <si>
+    <t>225713914315</t>
+  </si>
+  <si>
+    <t>225705885555</t>
+  </si>
+  <si>
+    <t>225102123827</t>
+  </si>
+  <si>
+    <t>225555980045</t>
+  </si>
+  <si>
+    <t>225158569514</t>
+  </si>
+  <si>
+    <t>225555674731</t>
+  </si>
+  <si>
+    <t>225503141520</t>
+  </si>
+  <si>
+    <t>225556135544</t>
+  </si>
+  <si>
+    <t>225564499952</t>
+  </si>
+  <si>
+    <t>225505444718</t>
+  </si>
+  <si>
+    <t>225508052455</t>
+  </si>
+  <si>
+    <t>225142859211</t>
+  </si>
+  <si>
+    <t>225101326666</t>
+  </si>
+  <si>
+    <t>225125554408</t>
+  </si>
+  <si>
+    <t>225707113939</t>
+  </si>
+  <si>
+    <t>225708181859</t>
+  </si>
+  <si>
+    <t>225707660599</t>
+  </si>
+  <si>
+    <t>225545876340</t>
+  </si>
+  <si>
+    <t>225556938613</t>
+  </si>
+  <si>
+    <t>225715152541</t>
+  </si>
+  <si>
+    <t>225718877596</t>
+  </si>
+  <si>
+    <t>225566136787</t>
+  </si>
+  <si>
+    <t>225564502321</t>
+  </si>
+  <si>
+    <t>225102730907</t>
+  </si>
+  <si>
+    <t>225769568776</t>
+  </si>
+  <si>
+    <t>225769106014</t>
+  </si>
+  <si>
+    <t>225505005491</t>
+  </si>
+  <si>
+    <t>225779020593</t>
+  </si>
+  <si>
+    <t>225707615352</t>
+  </si>
+  <si>
+    <t>225153270541</t>
+  </si>
+  <si>
+    <t>225153355182</t>
+  </si>
+  <si>
+    <t>225142085681</t>
+  </si>
+  <si>
+    <t>225757237489</t>
+  </si>
+  <si>
+    <t>225708637712</t>
+  </si>
+  <si>
+    <t>225545848633</t>
+  </si>
+  <si>
+    <t>225715578456</t>
+  </si>
+  <si>
+    <t>225787946260</t>
+  </si>
+  <si>
+    <t>225789711069</t>
+  </si>
+  <si>
+    <t>225778295499</t>
+  </si>
+  <si>
+    <t>225141452098</t>
+  </si>
+  <si>
+    <t>225757995568</t>
+  </si>
+  <si>
+    <t>225143251873</t>
+  </si>
+  <si>
+    <t>225709818381</t>
+  </si>
+  <si>
+    <t>225506916476</t>
+  </si>
+  <si>
+    <t>225747146398</t>
+  </si>
+  <si>
+    <t>225153174137</t>
+  </si>
+  <si>
+    <t>225707166403</t>
+  </si>
+  <si>
+    <t>225544200583</t>
+  </si>
+  <si>
+    <t>225708456868</t>
+  </si>
+  <si>
+    <t>225709326309</t>
+  </si>
+  <si>
+    <t>225748016426</t>
+  </si>
+  <si>
+    <t>225556297632</t>
+  </si>
+  <si>
+    <t>225142366967</t>
+  </si>
+  <si>
+    <t>225150827758</t>
+  </si>
+  <si>
+    <t>225547526336</t>
+  </si>
+  <si>
+    <t>225748539651</t>
+  </si>
+  <si>
+    <t>225789804207</t>
+  </si>
+  <si>
+    <t>225711845459</t>
+  </si>
+  <si>
+    <t>225749079876</t>
+  </si>
+  <si>
+    <t>225502420885</t>
+  </si>
+  <si>
+    <t>225503561835</t>
+  </si>
+  <si>
+    <t>225787237664</t>
+  </si>
+  <si>
+    <t>225544803606</t>
+  </si>
+  <si>
+    <t>225172080200</t>
+  </si>
+  <si>
+    <t>225707932859</t>
+  </si>
+  <si>
+    <t>225777470390</t>
+  </si>
+  <si>
+    <t>225140636475</t>
+  </si>
+  <si>
+    <t>225747923385</t>
+  </si>
+  <si>
+    <t>225757047590</t>
+  </si>
+  <si>
+    <t>225101516466</t>
+  </si>
+  <si>
+    <t>225779480000</t>
+  </si>
+  <si>
+    <t>225506795076</t>
+  </si>
+  <si>
+    <t>225564841650</t>
+  </si>
+  <si>
+    <t>225767861182</t>
+  </si>
+  <si>
+    <t>225707101767</t>
+  </si>
+  <si>
+    <t>225707671059</t>
+  </si>
+  <si>
+    <t>225560021012</t>
+  </si>
+  <si>
+    <t>225554466647</t>
+  </si>
+  <si>
+    <t>225160759241</t>
+  </si>
+  <si>
+    <t>225170008856</t>
+  </si>
+  <si>
+    <t>225711754362</t>
+  </si>
+  <si>
+    <t>225545536673</t>
+  </si>
+  <si>
+    <t>225102355807</t>
+  </si>
+  <si>
+    <t>225714331670</t>
+  </si>
+  <si>
+    <t>225708842044</t>
+  </si>
+  <si>
+    <t>225143423244</t>
+  </si>
+  <si>
+    <t>225555071595</t>
+  </si>
+  <si>
+    <t>225749057437</t>
+  </si>
+  <si>
+    <t>225102490136</t>
+  </si>
+  <si>
+    <t>225708989017</t>
+  </si>
+  <si>
+    <t>225153417242</t>
+  </si>
+  <si>
+    <t>225747128858</t>
+  </si>
+  <si>
+    <t>225707448981</t>
+  </si>
+  <si>
+    <t>225143752618</t>
+  </si>
+  <si>
+    <t>225540540525</t>
+  </si>
+  <si>
+    <t>225707552219</t>
+  </si>
+  <si>
+    <t>225507086049</t>
+  </si>
+  <si>
+    <t>225707778780</t>
+  </si>
+  <si>
+    <t>225101646680</t>
+  </si>
+  <si>
+    <t>225154541608</t>
+  </si>
+  <si>
+    <t>225107003435</t>
+  </si>
+  <si>
+    <t>225549491715</t>
+  </si>
+  <si>
+    <t>225102021418</t>
+  </si>
+  <si>
+    <t>225151524142</t>
+  </si>
+  <si>
+    <t>225544272544</t>
+  </si>
+  <si>
+    <t>225707304772</t>
+  </si>
+  <si>
+    <t>225150645021</t>
+  </si>
+  <si>
+    <t>225758247094</t>
+  </si>
+  <si>
+    <t>225779141598</t>
+  </si>
+  <si>
+    <t>225787590046</t>
+  </si>
+  <si>
+    <t>225505320121</t>
+  </si>
+  <si>
+    <t>225708964571</t>
+  </si>
+  <si>
+    <t>225505357528</t>
+  </si>
+  <si>
+    <t>225705444358</t>
+  </si>
+  <si>
+    <t>225152821414</t>
+  </si>
+  <si>
+    <t>225707468633</t>
+  </si>
+  <si>
+    <t>225118244473</t>
+  </si>
+  <si>
+    <t>225705015415</t>
+  </si>
+  <si>
+    <t>225545217995</t>
+  </si>
+  <si>
+    <t>225171992819</t>
+  </si>
+  <si>
+    <t>225140437004</t>
+  </si>
+  <si>
+    <t>225576178316</t>
+  </si>
+  <si>
+    <t>225544301963</t>
+  </si>
+  <si>
+    <t>225747089180</t>
+  </si>
+  <si>
+    <t>225501068079</t>
+  </si>
+  <si>
+    <t>225749273284</t>
+  </si>
+  <si>
+    <t>225708209108</t>
+  </si>
+  <si>
+    <t>225544113875</t>
+  </si>
+  <si>
+    <t>225507613012</t>
+  </si>
+  <si>
+    <t>225103257775</t>
+  </si>
+  <si>
+    <t>225102626346</t>
+  </si>
+  <si>
+    <t>225779595380</t>
+  </si>
+  <si>
+    <t>225758118469</t>
+  </si>
+  <si>
+    <t>225747904261</t>
+  </si>
+  <si>
+    <t>225544405582</t>
+  </si>
+  <si>
+    <t>225144491717</t>
+  </si>
+  <si>
+    <t>225171952527</t>
+  </si>
+  <si>
+    <t>225546202577</t>
+  </si>
+  <si>
+    <t>225788604235</t>
+  </si>
+  <si>
+    <t>225779750236</t>
+  </si>
+  <si>
+    <t>225757904498</t>
+  </si>
+  <si>
+    <t>225585044077</t>
+  </si>
+  <si>
+    <t>225797459540</t>
+  </si>
+  <si>
+    <t>225789134740</t>
+  </si>
+  <si>
+    <t>225173133025</t>
+  </si>
+  <si>
+    <t>225769922360</t>
+  </si>
+  <si>
+    <t>225779042853</t>
+  </si>
+  <si>
+    <t>225704266303</t>
+  </si>
+  <si>
+    <t>225769769597</t>
+  </si>
+  <si>
+    <t>225748144600</t>
+  </si>
+  <si>
+    <t>225500356045</t>
+  </si>
+  <si>
+    <t>225105262413</t>
+  </si>
+  <si>
+    <t>225152820003</t>
+  </si>
+  <si>
+    <t>225131325544</t>
+  </si>
+  <si>
+    <t>225508699344</t>
+  </si>
+  <si>
+    <t>225707797556</t>
+  </si>
+  <si>
+    <t>225143114908</t>
+  </si>
+  <si>
+    <t>225143986665</t>
+  </si>
+  <si>
+    <t>225788501422</t>
+  </si>
+  <si>
+    <t>225505753236</t>
+  </si>
+  <si>
+    <t>225767277084</t>
+  </si>
+  <si>
+    <t>225707803101</t>
+  </si>
+  <si>
+    <t>225748901701</t>
+  </si>
+  <si>
+    <t>225595125517</t>
+  </si>
+  <si>
+    <t>225708385889</t>
+  </si>
+  <si>
+    <t>225700221720</t>
+  </si>
+  <si>
+    <t>225576722516</t>
+  </si>
+  <si>
+    <t>225700528672</t>
+  </si>
+  <si>
+    <t>225140999846</t>
+  </si>
+  <si>
+    <t>225789098317</t>
+  </si>
+  <si>
+    <t>225172229425</t>
+  </si>
+  <si>
+    <t>225505449971</t>
+  </si>
+  <si>
+    <t>225505884988</t>
+  </si>
+  <si>
+    <t>225749707089</t>
+  </si>
+  <si>
+    <t>225576358473</t>
+  </si>
+  <si>
+    <t>225799644488</t>
+  </si>
+  <si>
+    <t>225103980756</t>
+  </si>
+  <si>
+    <t>225788014585</t>
+  </si>
+  <si>
+    <t>225789574066</t>
+  </si>
+  <si>
+    <t>225707144498</t>
+  </si>
+  <si>
+    <t>225140101866</t>
+  </si>
+  <si>
+    <t>225707820007</t>
+  </si>
+  <si>
+    <t>225767010416</t>
+  </si>
+  <si>
+    <t>225555504735</t>
+  </si>
+  <si>
+    <t>225566033374</t>
+  </si>
+  <si>
+    <t>225584191470</t>
+  </si>
+  <si>
+    <t>225701423449</t>
+  </si>
+  <si>
+    <t>225767750181</t>
+  </si>
+  <si>
+    <t>225160942339</t>
+  </si>
+  <si>
+    <t>225504279614</t>
+  </si>
+  <si>
+    <t>225501525653</t>
+  </si>
+  <si>
+    <t>225586506812</t>
+  </si>
+  <si>
+    <t>225798521680</t>
+  </si>
+  <si>
+    <t>225705408474</t>
+  </si>
+  <si>
+    <t>225545564020</t>
+  </si>
+  <si>
+    <t>225711754787</t>
+  </si>
+  <si>
+    <t>225716017586</t>
+  </si>
+  <si>
+    <t>225586996987</t>
+  </si>
+  <si>
+    <t>225704181883</t>
+  </si>
+  <si>
+    <t>225748847849</t>
+  </si>
+  <si>
+    <t>225748860906</t>
+  </si>
+  <si>
+    <t>225505180562</t>
+  </si>
+  <si>
+    <t>225556698184</t>
+  </si>
+  <si>
+    <t>225504900357</t>
+  </si>
+  <si>
+    <t>225506311662</t>
+  </si>
+  <si>
+    <t>225708213266</t>
+  </si>
+  <si>
+    <t>225506298995</t>
+  </si>
+  <si>
+    <t>225102226162</t>
+  </si>
+  <si>
+    <t>225566574551</t>
+  </si>
+  <si>
+    <t>225596669972</t>
+  </si>
+  <si>
+    <t>225508031865</t>
+  </si>
+  <si>
+    <t>225507579070</t>
+  </si>
+  <si>
+    <t>225705429781</t>
+  </si>
+  <si>
+    <t>225102520537</t>
+  </si>
+  <si>
+    <t>225708369428</t>
+  </si>
+  <si>
+    <t>225141090426</t>
+  </si>
+  <si>
+    <t>225554777555</t>
+  </si>
+  <si>
+    <t>225151867489</t>
+  </si>
+  <si>
+    <t>225554782792</t>
+  </si>
+  <si>
+    <t>225564726570</t>
+  </si>
+  <si>
+    <t>225142787881</t>
+  </si>
+  <si>
+    <t>225505502622</t>
+  </si>
+  <si>
+    <t>225142668613</t>
+  </si>
+  <si>
+    <t>225584208069</t>
+  </si>
+  <si>
+    <t>225758159980</t>
+  </si>
+  <si>
+    <t>225506711496</t>
+  </si>
+  <si>
+    <t>225142733049</t>
+  </si>
+  <si>
+    <t>225544107406</t>
+  </si>
+  <si>
+    <t>225505354643</t>
+  </si>
+  <si>
+    <t>225717187555</t>
+  </si>
+  <si>
+    <t>225101444416</t>
+  </si>
+  <si>
+    <t>225705448525</t>
+  </si>
+  <si>
+    <t>225105252544</t>
+  </si>
+  <si>
+    <t>225141747573</t>
+  </si>
+  <si>
+    <t>225703957602</t>
+  </si>
+  <si>
+    <t>225104446869</t>
+  </si>
+  <si>
+    <t>225504434110</t>
+  </si>
+  <si>
+    <t>225758289250</t>
+  </si>
+  <si>
+    <t>225585565036</t>
+  </si>
+  <si>
+    <t>225707426303</t>
+  </si>
+  <si>
+    <t>225141209925</t>
+  </si>
+  <si>
+    <t>225103989201</t>
+  </si>
+  <si>
+    <t>225504506396</t>
+  </si>
+  <si>
+    <t>225140423413</t>
+  </si>
+  <si>
+    <t>225747327317</t>
+  </si>
+  <si>
+    <t>225777081509</t>
+  </si>
+  <si>
+    <t>225759022933</t>
+  </si>
+  <si>
+    <t>225144175252</t>
+  </si>
+  <si>
+    <t>225102348275</t>
+  </si>
+  <si>
+    <t>225757681638</t>
+  </si>
+  <si>
+    <t>225152224906</t>
+  </si>
+  <si>
+    <t>225715936217</t>
+  </si>
+  <si>
+    <t>225502723488</t>
+  </si>
+  <si>
+    <t>225546105640</t>
+  </si>
+  <si>
+    <t>225505140414</t>
+  </si>
+  <si>
+    <t>225789471341</t>
+  </si>
+  <si>
+    <t>225566333932</t>
+  </si>
+  <si>
+    <t>225160996804</t>
+  </si>
+  <si>
+    <t>225101308463</t>
+  </si>
+  <si>
+    <t>225546105114</t>
+  </si>
+  <si>
+    <t>225160080476</t>
+  </si>
+  <si>
+    <t>225789058708</t>
+  </si>
+  <si>
+    <t>225758395665</t>
+  </si>
+  <si>
+    <t>225715398665</t>
+  </si>
+  <si>
+    <t>225674895040</t>
+  </si>
+  <si>
+    <t>225706035681</t>
+  </si>
+  <si>
+    <t>225707892929</t>
+  </si>
+  <si>
+    <t>225566696307</t>
+  </si>
+  <si>
+    <t>225505938581</t>
+  </si>
+  <si>
+    <t>225709902115</t>
+  </si>
+  <si>
+    <t>225153103448</t>
+  </si>
+  <si>
+    <t>225758203272</t>
+  </si>
+  <si>
+    <t>225787977500</t>
+  </si>
+  <si>
+    <t>225708056417</t>
+  </si>
+  <si>
+    <t>225708730755</t>
+  </si>
+  <si>
+    <t>225707472182</t>
+  </si>
+  <si>
+    <t>225584416018</t>
+  </si>
+  <si>
+    <t>225507948924</t>
+  </si>
+  <si>
+    <t>225152005247</t>
+  </si>
+  <si>
+    <t>225171686929</t>
+  </si>
+  <si>
+    <t>225708976792</t>
+  </si>
+  <si>
+    <t>225556541467</t>
+  </si>
+  <si>
+    <t>225160590174</t>
+  </si>
+  <si>
+    <t>225710014387</t>
+  </si>
+  <si>
+    <t>225711770630</t>
+  </si>
+  <si>
+    <t>225161304864</t>
+  </si>
+  <si>
+    <t>225504320429</t>
+  </si>
+  <si>
+    <t>225142404423</t>
+  </si>
+  <si>
+    <t>225545269326</t>
+  </si>
+  <si>
+    <t>225788889084</t>
+  </si>
+  <si>
+    <t>225141411407</t>
+  </si>
+  <si>
+    <t>225504291268</t>
+  </si>
+  <si>
+    <t>225709755045</t>
+  </si>
+  <si>
+    <t>225101516331</t>
+  </si>
+  <si>
+    <t>225505065016</t>
+  </si>
+  <si>
+    <t>225586623733</t>
+  </si>
+  <si>
+    <t>225778048385</t>
+  </si>
+  <si>
+    <t>225140636878</t>
+  </si>
+  <si>
+    <t>225708176165</t>
+  </si>
+  <si>
+    <t>225718343968</t>
+  </si>
+  <si>
+    <t>225153476646</t>
+  </si>
+  <si>
+    <t>225140419692</t>
+  </si>
+  <si>
+    <t>225153007822</t>
+  </si>
+  <si>
+    <t>225759192449</t>
+  </si>
+  <si>
+    <t>225749012329</t>
+  </si>
+  <si>
+    <t>225143619791</t>
+  </si>
+  <si>
+    <t>225708356524</t>
+  </si>
+  <si>
+    <t>225596102296</t>
+  </si>
+  <si>
+    <t>225503647184</t>
+  </si>
+  <si>
+    <t>225709813335</t>
+  </si>
+  <si>
+    <t>225504270466</t>
+  </si>
+  <si>
+    <t>225596108042</t>
+  </si>
+  <si>
+    <t>225707391194</t>
+  </si>
+  <si>
+    <t>225575502182</t>
+  </si>
+  <si>
+    <t>225769647653</t>
+  </si>
+  <si>
+    <t>225503391549</t>
+  </si>
+  <si>
+    <t>225505298865</t>
+  </si>
+  <si>
+    <t>225576883563</t>
+  </si>
+  <si>
+    <t>225504954511</t>
+  </si>
+  <si>
+    <t>225171402258</t>
+  </si>
+  <si>
+    <t>225505305842</t>
+  </si>
+  <si>
+    <t>225709007289</t>
+  </si>
+  <si>
+    <t>225565397414</t>
+  </si>
+  <si>
+    <t>225712520219</t>
+  </si>
+  <si>
+    <t>225141531267</t>
+  </si>
+  <si>
+    <t>225102166823</t>
+  </si>
+  <si>
+    <t>225501050852</t>
+  </si>
+  <si>
+    <t>225170585810</t>
+  </si>
+  <si>
+    <t>225585244266</t>
+  </si>
+  <si>
+    <t>225545099092</t>
+  </si>
+  <si>
+    <t>225768925338</t>
+  </si>
+  <si>
+    <t>225566160804</t>
+  </si>
+  <si>
+    <t>225505680589</t>
+  </si>
+  <si>
+    <t>225160827010</t>
+  </si>
+  <si>
+    <t>225788882699</t>
+  </si>
+  <si>
+    <t>225506955580</t>
+  </si>
+  <si>
+    <t>225142671746</t>
+  </si>
+  <si>
+    <t>225787186740</t>
+  </si>
+  <si>
+    <t>225501410753</t>
+  </si>
+  <si>
+    <t>225586965192</t>
+  </si>
+  <si>
+    <t>225153768996</t>
+  </si>
+  <si>
+    <t>225767739038</t>
+  </si>
+  <si>
+    <t>225171329793</t>
+  </si>
+  <si>
+    <t>225544560934</t>
+  </si>
+  <si>
+    <t>225706138129</t>
+  </si>
+  <si>
+    <t>225151901258</t>
+  </si>
+  <si>
+    <t>225757124146</t>
+  </si>
+  <si>
+    <t>225156723903</t>
+  </si>
+  <si>
+    <t>225720352566</t>
+  </si>
+  <si>
+    <t>225707890623</t>
+  </si>
+  <si>
+    <t>225747454866</t>
+  </si>
+  <si>
+    <t>225779476493</t>
+  </si>
+  <si>
+    <t>225709807962</t>
+  </si>
+  <si>
+    <t>225143827169</t>
+  </si>
+  <si>
+    <t>225708762325</t>
+  </si>
+  <si>
+    <t>225502278985</t>
+  </si>
+  <si>
+    <t>225170059666</t>
+  </si>
+  <si>
+    <t>225757498135</t>
+  </si>
+  <si>
+    <t>225103071057</t>
+  </si>
+  <si>
+    <t>225796696452</t>
+  </si>
+  <si>
+    <t>225784513640</t>
+  </si>
+  <si>
+    <t>225185869040</t>
+  </si>
+  <si>
+    <t>225556606100</t>
+  </si>
+  <si>
+    <t>225555825272</t>
+  </si>
+  <si>
+    <t>225102981617</t>
+  </si>
+  <si>
+    <t>225150524346</t>
+  </si>
+  <si>
+    <t>225140415253</t>
+  </si>
+  <si>
+    <t>225749137618</t>
+  </si>
+  <si>
+    <t>225502804391</t>
+  </si>
+  <si>
+    <t>225748521185</t>
+  </si>
+  <si>
+    <t>225052524443</t>
+  </si>
+  <si>
+    <t>225787887297</t>
+  </si>
+  <si>
+    <t>225142809190</t>
+  </si>
+  <si>
+    <t>225105643348</t>
+  </si>
+  <si>
+    <t>225150425884</t>
+  </si>
+  <si>
+    <t>225161604041</t>
+  </si>
+  <si>
+    <t>225708175247</t>
+  </si>
+  <si>
+    <t>225713540877</t>
+  </si>
+  <si>
+    <t>225787682604</t>
+  </si>
+  <si>
+    <t>225758028450</t>
+  </si>
+  <si>
+    <t>225779169882</t>
+  </si>
+  <si>
+    <t>225702024460</t>
+  </si>
+  <si>
+    <t>225103255143</t>
+  </si>
+  <si>
+    <t>225705026611</t>
+  </si>
+  <si>
+    <t>225797311827</t>
+  </si>
+  <si>
+    <t>225708791438</t>
+  </si>
+  <si>
+    <t>225171224051</t>
+  </si>
+  <si>
+    <t>225515456355</t>
+  </si>
+  <si>
+    <t>225789964112</t>
+  </si>
+  <si>
+    <t>225150343285</t>
+  </si>
+  <si>
+    <t>225150359320</t>
+  </si>
+  <si>
+    <t>225150375491</t>
+  </si>
+  <si>
+    <t>225555707289</t>
+  </si>
+  <si>
+    <t>225152877763</t>
+  </si>
+  <si>
+    <t>225752080944</t>
+  </si>
+  <si>
+    <t>225173471278</t>
+  </si>
+  <si>
+    <t>225769264640</t>
+  </si>
+  <si>
+    <t>225544636394</t>
+  </si>
+  <si>
+    <t>225574336118</t>
+  </si>
+  <si>
+    <t>225158800046</t>
+  </si>
+  <si>
+    <t>225769395486</t>
+  </si>
+  <si>
+    <t>225143636429</t>
+  </si>
+  <si>
+    <t>225105646480</t>
+  </si>
+  <si>
+    <t>225749541078</t>
+  </si>
+  <si>
+    <t>225566640046</t>
+  </si>
+  <si>
+    <t>225546454059</t>
+  </si>
+  <si>
+    <t>225161395079</t>
+  </si>
+  <si>
+    <t>225500335194</t>
+  </si>
+  <si>
+    <t>225160324899</t>
+  </si>
+  <si>
+    <t>225555721085</t>
+  </si>
+  <si>
+    <t>225708274679</t>
+  </si>
+  <si>
+    <t>225503672296</t>
+  </si>
+  <si>
+    <t>225595765254</t>
+  </si>
+  <si>
+    <t>225585060903</t>
+  </si>
+  <si>
+    <t>225777850516</t>
+  </si>
+  <si>
+    <t>225586097826</t>
+  </si>
+  <si>
+    <t>225554947941</t>
+  </si>
+  <si>
+    <t>225596456613</t>
+  </si>
+  <si>
+    <t>225555192367</t>
+  </si>
+  <si>
+    <t>225787882330</t>
+  </si>
+  <si>
+    <t>225707050117</t>
+  </si>
+  <si>
+    <t>225158580046</t>
+  </si>
+  <si>
+    <t>225707445512</t>
+  </si>
+  <si>
+    <t>225501552123</t>
+  </si>
+  <si>
+    <t>225107444612</t>
+  </si>
+  <si>
+    <t>225748042880</t>
+  </si>
+  <si>
+    <t>225779501991</t>
+  </si>
+  <si>
+    <t>225554762509</t>
+  </si>
+  <si>
+    <t>225100524016</t>
+  </si>
+  <si>
+    <t>225151118702</t>
+  </si>
+  <si>
+    <t>225788738955</t>
+  </si>
+  <si>
+    <t>225749593498</t>
+  </si>
+  <si>
+    <t>225747647144</t>
+  </si>
+  <si>
+    <t>225787266330</t>
+  </si>
+  <si>
+    <t>225714371221</t>
+  </si>
+  <si>
+    <t>225702881915</t>
+  </si>
+  <si>
+    <t>225749291932</t>
+  </si>
+  <si>
+    <t>225718761701</t>
+  </si>
+  <si>
+    <t>225708708017</t>
+  </si>
+  <si>
+    <t>225160618094</t>
+  </si>
+  <si>
+    <t>225768679295</t>
+  </si>
+  <si>
+    <t>225709879123</t>
+  </si>
+  <si>
+    <t>225706733590</t>
+  </si>
+  <si>
+    <t>225546487718</t>
+  </si>
+  <si>
+    <t>225595743537</t>
+  </si>
+  <si>
+    <t>225708054941</t>
+  </si>
+  <si>
+    <t>225705527431</t>
+  </si>
+  <si>
+    <t>225788246178</t>
+  </si>
+  <si>
+    <t>225104804450</t>
+  </si>
+  <si>
+    <t>225718508295</t>
+  </si>
+  <si>
+    <t>225707687007</t>
+  </si>
+  <si>
+    <t>225759275516</t>
+  </si>
+  <si>
+    <t>225707331327</t>
+  </si>
+  <si>
+    <t>225501787276</t>
+  </si>
+  <si>
+    <t>225140974202</t>
+  </si>
+  <si>
+    <t>225709127118</t>
+  </si>
+  <si>
+    <t>225707771590</t>
+  </si>
+  <si>
+    <t>225708822405</t>
+  </si>
+  <si>
+    <t>225140095191</t>
+  </si>
+  <si>
+    <t>225707829129</t>
+  </si>
+  <si>
+    <t>225152157410</t>
+  </si>
+  <si>
+    <t>225757346565</t>
+  </si>
+  <si>
+    <t>225508024496</t>
+  </si>
+  <si>
+    <t>225152858244</t>
+  </si>
+  <si>
+    <t>225704526052</t>
+  </si>
+  <si>
+    <t>225748731208</t>
+  </si>
+  <si>
+    <t>225574061065</t>
+  </si>
+  <si>
+    <t>225506414601</t>
+  </si>
+  <si>
+    <t>225546703176</t>
+  </si>
+  <si>
+    <t>225777075999</t>
+  </si>
+  <si>
+    <t>225574457063</t>
+  </si>
+  <si>
+    <t>225705245519</t>
+  </si>
+  <si>
+    <t>225759550356</t>
+  </si>
+  <si>
+    <t>225584168272</t>
+  </si>
+  <si>
+    <t>225565101838</t>
+  </si>
+  <si>
+    <t>225789513630</t>
+  </si>
+  <si>
+    <t>225709095586</t>
+  </si>
+  <si>
+    <t>225544357240</t>
+  </si>
+  <si>
+    <t>225180582534</t>
+  </si>
+  <si>
+    <t>225102944350</t>
+  </si>
+  <si>
+    <t>225767776709</t>
+  </si>
+  <si>
+    <t>225575283613</t>
+  </si>
+  <si>
+    <t>225555847266</t>
+  </si>
+  <si>
+    <t>225797108101</t>
+  </si>
+  <si>
+    <t>225566820153</t>
+  </si>
+  <si>
+    <t>225143552705</t>
+  </si>
+  <si>
+    <t>225152286105</t>
+  </si>
+  <si>
+    <t>225164645359</t>
+  </si>
+  <si>
+    <t>225101706202</t>
+  </si>
+  <si>
+    <t>225172125633</t>
+  </si>
+  <si>
+    <t>225749676307</t>
+  </si>
+  <si>
+    <t>225155668088</t>
+  </si>
+  <si>
+    <t>225566521271</t>
+  </si>
+  <si>
+    <t>225768838170</t>
+  </si>
+  <si>
+    <t>225789496648</t>
+  </si>
+  <si>
+    <t>225544924177</t>
+  </si>
+  <si>
+    <t>225789209093</t>
+  </si>
+  <si>
+    <t>225574390409</t>
+  </si>
+  <si>
+    <t>225704538793</t>
+  </si>
+  <si>
+    <t>225576644255</t>
+  </si>
+  <si>
+    <t>225757832821</t>
+  </si>
+  <si>
+    <t>225757061026</t>
+  </si>
+  <si>
+    <t>225777327269</t>
+  </si>
+  <si>
+    <t>225594841671</t>
+  </si>
+  <si>
+    <t>225777835240</t>
+  </si>
+  <si>
+    <t>225152296606</t>
+  </si>
+  <si>
+    <t>225503768718</t>
+  </si>
+  <si>
+    <t>225759901504</t>
+  </si>
+  <si>
+    <t>225101290309</t>
+  </si>
+  <si>
+    <t>225787398327</t>
+  </si>
+  <si>
+    <t>225768240111</t>
+  </si>
+  <si>
+    <t>225502805734</t>
+  </si>
+  <si>
+    <t>225152518904</t>
+  </si>
+  <si>
+    <t>225769270718</t>
+  </si>
+  <si>
+    <t>225565624892</t>
+  </si>
+  <si>
+    <t>225596788922</t>
+  </si>
+  <si>
+    <t>225142854877</t>
+  </si>
+  <si>
+    <t>225716624052</t>
+  </si>
+  <si>
+    <t>225544008778</t>
+  </si>
+  <si>
+    <t>225797691607</t>
+  </si>
+  <si>
+    <t>225757323541</t>
+  </si>
+  <si>
+    <t>225777123735</t>
+  </si>
+  <si>
+    <t>225788541480</t>
+  </si>
+  <si>
+    <t>225768953383</t>
+  </si>
+  <si>
+    <t>225787037833</t>
+  </si>
+  <si>
+    <t>225711962550</t>
+  </si>
+  <si>
+    <t>225544379794</t>
+  </si>
+  <si>
+    <t>225758654865</t>
+  </si>
+  <si>
+    <t>225788948342</t>
+  </si>
+  <si>
+    <t>225555233404</t>
+  </si>
+  <si>
+    <t>225564787971</t>
+  </si>
+  <si>
+    <t>225564619478</t>
+  </si>
+  <si>
+    <t>225706958567</t>
+  </si>
+  <si>
+    <t>225767060032</t>
+  </si>
+  <si>
+    <t>225702065060</t>
+  </si>
+  <si>
+    <t>225141968080</t>
+  </si>
+  <si>
+    <t>225767203062</t>
+  </si>
+  <si>
+    <t>225103279952</t>
+  </si>
+  <si>
+    <t>225595575373</t>
+  </si>
+  <si>
+    <t>225152410184</t>
+  </si>
+  <si>
+    <t>225142939970</t>
+  </si>
+  <si>
+    <t>225170276066</t>
+  </si>
+  <si>
+    <t>225715788341</t>
+  </si>
+  <si>
+    <t>225585791169</t>
+  </si>
+  <si>
+    <t>225759158067</t>
+  </si>
+  <si>
+    <t>225596910363</t>
+  </si>
+  <si>
+    <t>225584131164</t>
+  </si>
+  <si>
+    <t>225502209789</t>
+  </si>
+  <si>
+    <t>225103090620</t>
+  </si>
+  <si>
+    <t>225767784424</t>
+  </si>
+  <si>
+    <t>225596257398</t>
+  </si>
+  <si>
+    <t>225711359029</t>
+  </si>
+  <si>
+    <t>225545140708</t>
+  </si>
+  <si>
+    <t>225788622658</t>
+  </si>
+  <si>
+    <t>225711460247</t>
+  </si>
+  <si>
+    <t>225502960004</t>
+  </si>
+  <si>
+    <t>225545875039</t>
+  </si>
+  <si>
+    <t>225502859815</t>
+  </si>
+  <si>
+    <t>225555046622</t>
+  </si>
+  <si>
+    <t>225787699706</t>
+  </si>
+  <si>
+    <t>225708534055</t>
+  </si>
+  <si>
+    <t>225720705122</t>
+  </si>
+  <si>
+    <t>225768449097</t>
+  </si>
+  <si>
+    <t>225712789428</t>
+  </si>
+  <si>
+    <t>225798168791</t>
+  </si>
+  <si>
+    <t>225595322093</t>
+  </si>
+  <si>
+    <t>225586889693</t>
+  </si>
+  <si>
+    <t>225104045582</t>
+  </si>
+  <si>
+    <t>225707280799</t>
+  </si>
+  <si>
+    <t>225505015566</t>
+  </si>
+  <si>
+    <t>225564423126</t>
+  </si>
+  <si>
+    <t>225797702700</t>
+  </si>
+  <si>
+    <t>225101454512</t>
+  </si>
+  <si>
+    <t>225505609696</t>
+  </si>
+  <si>
+    <t>225101247791</t>
+  </si>
+  <si>
+    <t>225777249964</t>
+  </si>
+  <si>
+    <t>225565784231</t>
+  </si>
+  <si>
+    <t>225556646392</t>
+  </si>
+  <si>
+    <t>225584077365</t>
+  </si>
+  <si>
+    <t>225778783911</t>
+  </si>
+  <si>
+    <t>225787600024</t>
+  </si>
+  <si>
+    <t>225749313078</t>
+  </si>
+  <si>
+    <t>225703318647</t>
+  </si>
+  <si>
+    <t>225797686233</t>
+  </si>
+  <si>
+    <t>225555512374</t>
+  </si>
+  <si>
+    <t>225507378795</t>
+  </si>
+  <si>
+    <t>225566967477</t>
+  </si>
+  <si>
+    <t>225584959120</t>
+  </si>
+  <si>
+    <t>225504300642</t>
+  </si>
+  <si>
+    <t>225595619599</t>
+  </si>
+  <si>
+    <t>225173960626</t>
+  </si>
+  <si>
+    <t>225151383541</t>
+  </si>
+  <si>
+    <t>225555913421</t>
+  </si>
+  <si>
+    <t>225748868635</t>
+  </si>
+  <si>
+    <t>225594830423</t>
+  </si>
+  <si>
+    <t>225505548489</t>
+  </si>
+  <si>
+    <t>225585602525</t>
+  </si>
+  <si>
+    <t>225788753542</t>
+  </si>
+  <si>
+    <t>225171747461</t>
+  </si>
+  <si>
+    <t>225566106316</t>
+  </si>
+  <si>
+    <t>225767189881</t>
+  </si>
+  <si>
+    <t>225779475774</t>
+  </si>
+  <si>
+    <t>225585392957</t>
+  </si>
+  <si>
+    <t>225575274913</t>
+  </si>
+  <si>
+    <t>225749011875</t>
+  </si>
+  <si>
+    <t>225779237336</t>
+  </si>
+  <si>
+    <t>225574435082</t>
+  </si>
+  <si>
+    <t>225101687469</t>
+  </si>
+  <si>
+    <t>225701487439</t>
+  </si>
+  <si>
+    <t>225758610459</t>
+  </si>
+  <si>
+    <t>225555160381</t>
+  </si>
+  <si>
+    <t>225709303120</t>
+  </si>
+  <si>
+    <t>225125869235</t>
+  </si>
+  <si>
+    <t>225155121236</t>
+  </si>
+  <si>
+    <t>225070505446</t>
+  </si>
+  <si>
+    <t>225744405296</t>
+  </si>
+  <si>
+    <t>225194435508</t>
+  </si>
+  <si>
+    <t>225140508713</t>
+  </si>
+  <si>
+    <t>225705026464</t>
+  </si>
+  <si>
+    <t>225556462410</t>
+  </si>
+  <si>
+    <t>225707906655</t>
+  </si>
+  <si>
+    <t>225529472103</t>
+  </si>
+  <si>
+    <t>225106642854</t>
+  </si>
+  <si>
+    <t>225788980690</t>
+  </si>
+  <si>
+    <t>225778555549</t>
+  </si>
+  <si>
+    <t>225151506362</t>
+  </si>
+  <si>
+    <t>225140194085</t>
+  </si>
+  <si>
+    <t>225552844108</t>
+  </si>
+  <si>
+    <t>225506482029</t>
+  </si>
+  <si>
+    <t>225787617297</t>
+  </si>
+  <si>
+    <t>225160828255</t>
+  </si>
+  <si>
+    <t>225594706486</t>
+  </si>
+  <si>
+    <t>225102122414</t>
+  </si>
+  <si>
+    <t>225708345602</t>
+  </si>
+  <si>
+    <t>225758201607</t>
+  </si>
+  <si>
+    <t>225709361478</t>
+  </si>
+  <si>
+    <t>225506613483</t>
+  </si>
+  <si>
+    <t>225709084664</t>
+  </si>
+  <si>
+    <t>225501172768</t>
+  </si>
+  <si>
+    <t>225768799777</t>
+  </si>
+  <si>
+    <t>225711932631</t>
+  </si>
+  <si>
+    <t>225777086918</t>
+  </si>
+  <si>
+    <t>225140220974</t>
+  </si>
+  <si>
+    <t>225759595567</t>
+  </si>
+  <si>
+    <t>225747585035</t>
+  </si>
+  <si>
+    <t>225747412695</t>
+  </si>
+  <si>
+    <t>225757201996</t>
+  </si>
+  <si>
+    <t>225739069317</t>
+  </si>
+  <si>
+    <t>225554174165</t>
+  </si>
+  <si>
+    <t>225540982315</t>
+  </si>
+  <si>
+    <t>225505049984</t>
+  </si>
+  <si>
+    <t>225584156483</t>
+  </si>
+  <si>
+    <t>225574166660</t>
+  </si>
+  <si>
+    <t>225500912461</t>
+  </si>
+  <si>
+    <t>225707990047</t>
+  </si>
+  <si>
+    <t>225554632476</t>
+  </si>
+  <si>
+    <t>225160071162</t>
+  </si>
+  <si>
+    <t>225102908665</t>
+  </si>
+  <si>
+    <t>225711661622</t>
+  </si>
+  <si>
+    <t>225779883605</t>
+  </si>
+  <si>
+    <t>225758953799</t>
+  </si>
+  <si>
+    <t>225565598437</t>
+  </si>
+  <si>
+    <t>225719799275</t>
+  </si>
+  <si>
+    <t>225707824268</t>
+  </si>
+  <si>
+    <t>225153481815</t>
+  </si>
+  <si>
+    <t>225101782697</t>
+  </si>
+  <si>
+    <t>225575631273</t>
+  </si>
+  <si>
+    <t>225160236285</t>
+  </si>
+  <si>
+    <t>225176356365</t>
   </si>
   <si>
     <t>18-39 ans</t>
